--- a/grupos/2BLCM - Estadisticos 20222.xlsx
+++ b/grupos/2BLCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="177">
   <si>
     <t>Materia</t>
   </si>
@@ -1035,7 +1035,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>-1</v>
@@ -1044,10 +1044,10 @@
         <v>7</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -1089,7 +1089,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -1098,10 +1098,10 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -1112,7 +1112,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>-1</v>
@@ -1121,10 +1121,10 @@
         <v>8</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G5">
         <v>7</v>
@@ -1166,7 +1166,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1175,10 +1175,10 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -1189,7 +1189,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>-1</v>
@@ -1198,10 +1198,10 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -1243,7 +1243,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1252,10 +1252,10 @@
         <v>5</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1266,7 +1266,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>-1</v>
@@ -1275,10 +1275,10 @@
         <v>6</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -1320,7 +1320,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1329,10 +1329,10 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1343,7 +1343,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>-1</v>
@@ -1352,10 +1352,10 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -1397,7 +1397,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1406,10 +1406,10 @@
         <v>5</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1420,7 +1420,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <v>-1</v>
@@ -1429,10 +1429,10 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G9">
         <v>6</v>
@@ -1474,7 +1474,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1483,10 +1483,10 @@
         <v>5</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1497,7 +1497,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>-1</v>
@@ -1506,10 +1506,10 @@
         <v>5</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -1551,7 +1551,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1560,10 +1560,10 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1574,7 +1574,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C11">
         <v>-1</v>
@@ -1583,10 +1583,10 @@
         <v>6</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>8</v>
@@ -1628,7 +1628,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1637,10 +1637,10 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1651,7 +1651,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C12">
         <v>-1</v>
@@ -1660,10 +1660,10 @@
         <v>10</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -1705,7 +1705,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1714,10 +1714,10 @@
         <v>10</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1728,7 +1728,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>-1</v>
@@ -1737,10 +1737,10 @@
         <v>8</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13">
         <v>6</v>
@@ -1782,7 +1782,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1791,10 +1791,10 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1805,7 +1805,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>-1</v>
@@ -1814,10 +1814,10 @@
         <v>6</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G14">
         <v>7</v>
@@ -1859,7 +1859,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1868,10 +1868,10 @@
         <v>6</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1882,7 +1882,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>-1</v>
@@ -1891,10 +1891,10 @@
         <v>6</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G15">
         <v>6</v>
@@ -1936,7 +1936,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1945,10 +1945,10 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -1959,7 +1959,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C16">
         <v>-1</v>
@@ -1968,10 +1968,10 @@
         <v>6</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G16">
         <v>6</v>
@@ -2013,7 +2013,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -2022,10 +2022,10 @@
         <v>6</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -2036,7 +2036,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>-1</v>
@@ -2045,10 +2045,10 @@
         <v>5</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>3</v>
@@ -2090,7 +2090,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2099,10 +2099,10 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -2113,7 +2113,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C18">
         <v>-1</v>
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G18">
         <v>6</v>
@@ -2167,7 +2167,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2176,10 +2176,10 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2190,7 +2190,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C19">
         <v>-1</v>
@@ -2199,10 +2199,10 @@
         <v>10</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>10</v>
@@ -2244,7 +2244,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2253,10 +2253,10 @@
         <v>10</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -2267,7 +2267,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>-1</v>
@@ -2276,10 +2276,10 @@
         <v>6</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>8</v>
@@ -2321,7 +2321,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2330,10 +2330,10 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2344,7 +2344,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C21">
         <v>-1</v>
@@ -2353,10 +2353,10 @@
         <v>5</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G21">
         <v>3</v>
@@ -2398,7 +2398,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2407,10 +2407,10 @@
         <v>5</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2421,7 +2421,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>-1</v>
@@ -2430,10 +2430,10 @@
         <v>5</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2475,7 +2475,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2484,10 +2484,10 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2498,7 +2498,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C23">
         <v>-1</v>
@@ -2507,10 +2507,10 @@
         <v>5</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -2552,7 +2552,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2561,10 +2561,10 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2575,7 +2575,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C24">
         <v>-1</v>
@@ -2584,10 +2584,10 @@
         <v>10</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>10</v>
@@ -2629,7 +2629,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2638,10 +2638,10 @@
         <v>10</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2652,7 +2652,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>-1</v>
@@ -2661,10 +2661,10 @@
         <v>5</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G25">
         <v>6</v>
@@ -2706,7 +2706,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2715,10 +2715,10 @@
         <v>5</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>6</v>
@@ -2729,7 +2729,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>-1</v>
@@ -2738,10 +2738,10 @@
         <v>6</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G26">
         <v>8</v>
@@ -2783,7 +2783,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2792,10 +2792,10 @@
         <v>6</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2806,7 +2806,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C27">
         <v>-1</v>
@@ -2815,10 +2815,10 @@
         <v>8</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G27">
         <v>6</v>
@@ -2860,7 +2860,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -2869,10 +2869,10 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -2883,7 +2883,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C28">
         <v>-1</v>
@@ -2892,10 +2892,10 @@
         <v>8</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>7</v>
@@ -2937,7 +2937,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -2946,10 +2946,10 @@
         <v>8</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2960,7 +2960,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C29">
         <v>-1</v>
@@ -2969,10 +2969,10 @@
         <v>6</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G29">
         <v>6</v>
@@ -3014,7 +3014,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3023,10 +3023,10 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -3037,7 +3037,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C30">
         <v>-1</v>
@@ -3046,10 +3046,10 @@
         <v>6</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G30">
         <v>7</v>
@@ -3091,7 +3091,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3100,10 +3100,10 @@
         <v>6</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3114,7 +3114,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>-1</v>
@@ -3123,10 +3123,10 @@
         <v>5</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G31">
         <v>6</v>
@@ -3168,7 +3168,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3177,10 +3177,10 @@
         <v>5</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y31">
         <v>6</v>
@@ -3191,7 +3191,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C32">
         <v>-1</v>
@@ -3200,10 +3200,10 @@
         <v>10</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G32">
         <v>8</v>
@@ -3245,7 +3245,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3254,10 +3254,10 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3268,7 +3268,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C33">
         <v>-1</v>
@@ -3277,10 +3277,10 @@
         <v>10</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G33">
         <v>7</v>
@@ -3322,7 +3322,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3331,10 +3331,10 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3345,7 +3345,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C34">
         <v>-1</v>
@@ -3354,10 +3354,10 @@
         <v>6</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G34">
         <v>8</v>
@@ -3399,7 +3399,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3408,10 +3408,10 @@
         <v>6</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -3422,7 +3422,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C35">
         <v>-1</v>
@@ -3431,10 +3431,10 @@
         <v>5</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -3476,7 +3476,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3485,10 +3485,10 @@
         <v>5</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -3499,7 +3499,7 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C36">
         <v>-1</v>
@@ -3508,10 +3508,10 @@
         <v>5</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -3553,7 +3553,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>-1</v>
@@ -3562,10 +3562,10 @@
         <v>5</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -3576,7 +3576,7 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C37">
         <v>-1</v>
@@ -3585,10 +3585,10 @@
         <v>6</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G37">
         <v>7</v>
@@ -3630,7 +3630,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U37">
         <v>-1</v>
@@ -3639,10 +3639,10 @@
         <v>6</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y37">
         <v>7</v>
@@ -3653,7 +3653,7 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C38">
         <v>-1</v>
@@ -3662,10 +3662,10 @@
         <v>8</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -3707,7 +3707,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U38">
         <v>-1</v>
@@ -3716,10 +3716,10 @@
         <v>8</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y38">
         <v>5</v>
@@ -3730,7 +3730,7 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C39">
         <v>-1</v>
@@ -3739,10 +3739,10 @@
         <v>5</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -3784,7 +3784,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U39">
         <v>-1</v>
@@ -3793,10 +3793,10 @@
         <v>5</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y39">
         <v>5</v>
@@ -3807,7 +3807,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>-1</v>
@@ -3816,10 +3816,10 @@
         <v>5</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -3861,7 +3861,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>-1</v>
@@ -3870,10 +3870,10 @@
         <v>5</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -3884,7 +3884,7 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C41">
         <v>-1</v>
@@ -3893,10 +3893,10 @@
         <v>7</v>
       </c>
       <c r="E41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G41">
         <v>7</v>
@@ -3938,7 +3938,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U41">
         <v>-1</v>
@@ -3947,10 +3947,10 @@
         <v>7</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y41">
         <v>7</v>
@@ -3961,7 +3961,7 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C42">
         <v>-1</v>
@@ -3970,10 +3970,10 @@
         <v>8</v>
       </c>
       <c r="E42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G42">
         <v>8</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U42">
         <v>-1</v>
@@ -4024,10 +4024,10 @@
         <v>8</v>
       </c>
       <c r="W42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y42">
         <v>8</v>
@@ -4038,7 +4038,7 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C43">
         <v>-1</v>
@@ -4047,10 +4047,10 @@
         <v>9</v>
       </c>
       <c r="E43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G43">
         <v>8</v>
@@ -4092,7 +4092,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U43">
         <v>-1</v>
@@ -4101,10 +4101,10 @@
         <v>9</v>
       </c>
       <c r="W43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y43">
         <v>8</v>
@@ -4115,7 +4115,7 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C44">
         <v>-1</v>
@@ -4124,10 +4124,10 @@
         <v>7</v>
       </c>
       <c r="E44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G44">
         <v>7</v>
@@ -4169,7 +4169,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U44">
         <v>-1</v>
@@ -4178,10 +4178,10 @@
         <v>7</v>
       </c>
       <c r="W44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y44">
         <v>7</v>
@@ -4302,7 +4302,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -4311,10 +4311,10 @@
         <v>120</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -4361,7 +4361,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -4370,10 +4370,10 @@
         <v>115</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -4420,7 +4420,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -4429,10 +4429,10 @@
         <v>70</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>75</v>
@@ -4479,7 +4479,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -4488,10 +4488,10 @@
         <v>110</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>91.7</v>
@@ -4538,7 +4538,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -4547,10 +4547,10 @@
         <v>120</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>95</v>
@@ -4597,7 +4597,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -4606,10 +4606,10 @@
         <v>110</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>88.3</v>
@@ -4656,7 +4656,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -4665,10 +4665,10 @@
         <v>70</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G10">
         <v>66.7</v>
@@ -4715,7 +4715,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -4724,10 +4724,10 @@
         <v>120</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -4774,7 +4774,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -4783,10 +4783,10 @@
         <v>120</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -4833,7 +4833,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>120</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -4892,7 +4892,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -4901,10 +4901,10 @@
         <v>120</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>100</v>
@@ -4951,7 +4951,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -4960,10 +4960,10 @@
         <v>120</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G15">
         <v>81.7</v>
@@ -5010,7 +5010,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -5019,10 +5019,10 @@
         <v>120</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>98.3</v>
@@ -5069,7 +5069,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>90</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G17">
         <v>85</v>
@@ -5128,7 +5128,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -5137,10 +5137,10 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>100</v>
@@ -5187,7 +5187,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -5196,10 +5196,10 @@
         <v>120</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -5246,7 +5246,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -5255,10 +5255,10 @@
         <v>120</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>100</v>
@@ -5305,7 +5305,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -5314,10 +5314,10 @@
         <v>110</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G21">
         <v>88.3</v>
@@ -5364,7 +5364,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -5373,10 +5373,10 @@
         <v>60</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>83.3</v>
@@ -5423,7 +5423,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -5432,10 +5432,10 @@
         <v>110</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="G23">
         <v>88.3</v>
@@ -5482,7 +5482,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -5491,10 +5491,10 @@
         <v>120</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -5541,7 +5541,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -5550,10 +5550,10 @@
         <v>95</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G25">
         <v>88.3</v>
@@ -5600,7 +5600,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -5609,10 +5609,10 @@
         <v>120</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26">
         <v>100</v>
@@ -5659,7 +5659,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -5668,10 +5668,10 @@
         <v>120</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -5718,7 +5718,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>120</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>100</v>
@@ -5777,7 +5777,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -5786,10 +5786,10 @@
         <v>120</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G29">
         <v>95</v>
@@ -5836,7 +5836,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -5845,10 +5845,10 @@
         <v>120</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>100</v>
@@ -5895,7 +5895,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -5904,10 +5904,10 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="G31">
         <v>83.3</v>
@@ -5954,7 +5954,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -5963,10 +5963,10 @@
         <v>120</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>100</v>
@@ -6013,7 +6013,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -6022,10 +6022,10 @@
         <v>120</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>100</v>
@@ -6072,7 +6072,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -6081,10 +6081,10 @@
         <v>120</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>100</v>
@@ -6131,7 +6131,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -6140,10 +6140,10 @@
         <v>120</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G35">
         <v>100</v>
@@ -6190,7 +6190,7 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -6199,10 +6199,10 @@
         <v>120</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G36">
         <v>100</v>
@@ -6249,7 +6249,7 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>120</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G37">
         <v>100</v>
@@ -6308,7 +6308,7 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -6317,10 +6317,10 @@
         <v>110</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G38">
         <v>100</v>
@@ -6367,7 +6367,7 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -6376,10 +6376,10 @@
         <v>120</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G39">
         <v>100</v>
@@ -6426,7 +6426,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -6435,10 +6435,10 @@
         <v>110</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G40">
         <v>88.3</v>
@@ -6485,7 +6485,7 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>120</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G41">
         <v>100</v>
@@ -6544,7 +6544,7 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -6553,10 +6553,10 @@
         <v>120</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42">
         <v>100</v>
@@ -6603,7 +6603,7 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -6612,10 +6612,10 @@
         <v>120</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G43">
         <v>100</v>
@@ -6662,7 +6662,7 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -6671,10 +6671,10 @@
         <v>120</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G44">
         <v>85</v>
@@ -6768,7 +6768,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -6797,7 +6797,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -6806,27 +6806,30 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>34.15</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
       </c>
       <c r="I3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -6835,56 +6838,62 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>73.17</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>26.83</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
       </c>
       <c r="I4">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5">
         <v>41</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>78.05</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>21.95</v>
+      </c>
+      <c r="H5">
+        <v>6.8</v>
       </c>
       <c r="I5">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -6893,19 +6902,19 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>65.84999999999999</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="G6">
-        <v>34.15</v>
+        <v>17.07</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6916,28 +6925,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7">
         <v>41</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>73.17</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="G7">
-        <v>26.83</v>
+        <v>17.07</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6953,7 +6962,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F165"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6994,7 +7003,7 @@
         <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>65</v>
@@ -7002,16 +7011,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920124</v>
+        <v>22330051920343</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -7022,19 +7031,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920124</v>
+        <v>22330051920342</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>65</v>
@@ -7042,39 +7051,39 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920124</v>
+        <v>22330051920125</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920343</v>
+        <v>22330051920126</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>65</v>
@@ -7082,16 +7091,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920343</v>
+        <v>22330051920344</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -7102,19 +7111,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920343</v>
+        <v>22330051920127</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>65</v>
@@ -7122,39 +7131,39 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920343</v>
+        <v>22330051920424</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920342</v>
+        <v>22330051920345</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>65</v>
@@ -7162,16 +7171,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920342</v>
+        <v>22330051920128</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -7182,19 +7191,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920342</v>
+        <v>22330051920130</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>65</v>
@@ -7202,39 +7211,39 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920342</v>
+        <v>22330051920131</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920125</v>
+        <v>22330051920132</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
         <v>65</v>
@@ -7242,16 +7251,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920125</v>
+        <v>22330051920133</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -7262,19 +7271,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920125</v>
+        <v>22330051920134</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
         <v>65</v>
@@ -7282,39 +7291,39 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920125</v>
+        <v>22330051920135</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920126</v>
+        <v>22330051920244</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>65</v>
@@ -7322,16 +7331,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920126</v>
+        <v>22330051920346</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
@@ -7342,19 +7351,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920126</v>
+        <v>22330051920129</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E20" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
         <v>65</v>
@@ -7362,39 +7371,39 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>22330051920126</v>
+        <v>22330051920247</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>22330051920344</v>
+        <v>22330051920347</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
         <v>65</v>
@@ -7402,16 +7411,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>22330051920344</v>
+        <v>22330051920136</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
@@ -7422,19 +7431,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>22330051920344</v>
+        <v>22330051920349</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
         <v>65</v>
@@ -7442,39 +7451,39 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>22330051920344</v>
+        <v>22330051920137</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>22330051920127</v>
+        <v>22330051920350</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
         <v>65</v>
@@ -7482,16 +7491,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>22330051920127</v>
+        <v>22330051920138</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="E27" t="s">
         <v>6</v>
@@ -7502,19 +7511,19 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>22330051920127</v>
+        <v>22330051920110</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="E28" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" t="s">
         <v>65</v>
@@ -7522,39 +7531,39 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>22330051920127</v>
+        <v>22330051920140</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>22330051920424</v>
+        <v>22330051920352</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
         <v>65</v>
@@ -7562,16 +7571,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>22330051920424</v>
+        <v>22330051920252</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="E31" t="s">
         <v>6</v>
@@ -7582,19 +7591,19 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>22330051920424</v>
+        <v>22330051920142</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D32" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="E32" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32" t="s">
         <v>65</v>
@@ -7602,39 +7611,39 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>22330051920424</v>
+        <v>22330051920353</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D33" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>22330051920345</v>
+        <v>22330051920354</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="D34" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F34" t="s">
         <v>65</v>
@@ -7642,16 +7651,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>22330051920345</v>
+        <v>22330051920143</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
         <v>110</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="E35" t="s">
         <v>6</v>
@@ -7662,19 +7671,19 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>22330051920345</v>
+        <v>22330051920144</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="D36" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="E36" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" t="s">
         <v>65</v>
@@ -7682,39 +7691,39 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>22330051920345</v>
+        <v>22330051920145</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="D37" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>22330051920128</v>
+        <v>22330051920146</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F38" t="s">
         <v>65</v>
@@ -7722,16 +7731,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>22330051920128</v>
+        <v>22330051920258</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C39" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D39" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="E39" t="s">
         <v>6</v>
@@ -7742,19 +7751,19 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>22330051920128</v>
+        <v>22330051920355</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="C40" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="E40" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F40" t="s">
         <v>65</v>
@@ -7762,2502 +7771,42 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>22330051920128</v>
+        <v>22330051920147</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C41" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="D41" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>22330051920130</v>
+        <v>22330051920148</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="D42" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="E42" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F42" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>22330051920130</v>
-      </c>
-      <c r="B43" t="s">
-        <v>81</v>
-      </c>
-      <c r="C43" t="s">
-        <v>114</v>
-      </c>
-      <c r="D43" t="s">
-        <v>146</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>22330051920130</v>
-      </c>
-      <c r="B44" t="s">
-        <v>81</v>
-      </c>
-      <c r="C44" t="s">
-        <v>114</v>
-      </c>
-      <c r="D44" t="s">
-        <v>146</v>
-      </c>
-      <c r="E44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>22330051920130</v>
-      </c>
-      <c r="B45" t="s">
-        <v>81</v>
-      </c>
-      <c r="C45" t="s">
-        <v>114</v>
-      </c>
-      <c r="D45" t="s">
-        <v>146</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>22330051920131</v>
-      </c>
-      <c r="B46" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" t="s">
-        <v>115</v>
-      </c>
-      <c r="D46" t="s">
-        <v>147</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>22330051920131</v>
-      </c>
-      <c r="B47" t="s">
-        <v>82</v>
-      </c>
-      <c r="C47" t="s">
-        <v>115</v>
-      </c>
-      <c r="D47" t="s">
-        <v>147</v>
-      </c>
-      <c r="E47" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>22330051920131</v>
-      </c>
-      <c r="B48" t="s">
-        <v>82</v>
-      </c>
-      <c r="C48" t="s">
-        <v>115</v>
-      </c>
-      <c r="D48" t="s">
-        <v>147</v>
-      </c>
-      <c r="E48" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>22330051920131</v>
-      </c>
-      <c r="B49" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" t="s">
-        <v>115</v>
-      </c>
-      <c r="D49" t="s">
-        <v>147</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>22330051920132</v>
-      </c>
-      <c r="B50" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" t="s">
-        <v>86</v>
-      </c>
-      <c r="D50" t="s">
-        <v>148</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>22330051920132</v>
-      </c>
-      <c r="B51" t="s">
-        <v>83</v>
-      </c>
-      <c r="C51" t="s">
-        <v>86</v>
-      </c>
-      <c r="D51" t="s">
-        <v>148</v>
-      </c>
-      <c r="E51" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>22330051920132</v>
-      </c>
-      <c r="B52" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" t="s">
-        <v>86</v>
-      </c>
-      <c r="D52" t="s">
-        <v>148</v>
-      </c>
-      <c r="E52" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>22330051920132</v>
-      </c>
-      <c r="B53" t="s">
-        <v>83</v>
-      </c>
-      <c r="C53" t="s">
-        <v>86</v>
-      </c>
-      <c r="D53" t="s">
-        <v>148</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>22330051920133</v>
-      </c>
-      <c r="B54" t="s">
-        <v>84</v>
-      </c>
-      <c r="C54" t="s">
-        <v>104</v>
-      </c>
-      <c r="D54" t="s">
-        <v>149</v>
-      </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>22330051920133</v>
-      </c>
-      <c r="B55" t="s">
-        <v>84</v>
-      </c>
-      <c r="C55" t="s">
-        <v>104</v>
-      </c>
-      <c r="D55" t="s">
-        <v>149</v>
-      </c>
-      <c r="E55" t="s">
-        <v>6</v>
-      </c>
-      <c r="F55" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>22330051920133</v>
-      </c>
-      <c r="B56" t="s">
-        <v>84</v>
-      </c>
-      <c r="C56" t="s">
-        <v>104</v>
-      </c>
-      <c r="D56" t="s">
-        <v>149</v>
-      </c>
-      <c r="E56" t="s">
-        <v>5</v>
-      </c>
-      <c r="F56" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>22330051920133</v>
-      </c>
-      <c r="B57" t="s">
-        <v>84</v>
-      </c>
-      <c r="C57" t="s">
-        <v>104</v>
-      </c>
-      <c r="D57" t="s">
-        <v>149</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>22330051920134</v>
-      </c>
-      <c r="B58" t="s">
-        <v>85</v>
-      </c>
-      <c r="C58" t="s">
-        <v>116</v>
-      </c>
-      <c r="D58" t="s">
-        <v>150</v>
-      </c>
-      <c r="E58" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>22330051920134</v>
-      </c>
-      <c r="B59" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" t="s">
-        <v>116</v>
-      </c>
-      <c r="D59" t="s">
-        <v>150</v>
-      </c>
-      <c r="E59" t="s">
-        <v>6</v>
-      </c>
-      <c r="F59" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>22330051920134</v>
-      </c>
-      <c r="B60" t="s">
-        <v>85</v>
-      </c>
-      <c r="C60" t="s">
-        <v>116</v>
-      </c>
-      <c r="D60" t="s">
-        <v>150</v>
-      </c>
-      <c r="E60" t="s">
-        <v>5</v>
-      </c>
-      <c r="F60" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>22330051920134</v>
-      </c>
-      <c r="B61" t="s">
-        <v>85</v>
-      </c>
-      <c r="C61" t="s">
-        <v>116</v>
-      </c>
-      <c r="D61" t="s">
-        <v>150</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>22330051920135</v>
-      </c>
-      <c r="B62" t="s">
-        <v>86</v>
-      </c>
-      <c r="C62" t="s">
-        <v>112</v>
-      </c>
-      <c r="D62" t="s">
-        <v>151</v>
-      </c>
-      <c r="E62" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>22330051920135</v>
-      </c>
-      <c r="B63" t="s">
-        <v>86</v>
-      </c>
-      <c r="C63" t="s">
-        <v>112</v>
-      </c>
-      <c r="D63" t="s">
-        <v>151</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>22330051920135</v>
-      </c>
-      <c r="B64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C64" t="s">
-        <v>112</v>
-      </c>
-      <c r="D64" t="s">
-        <v>151</v>
-      </c>
-      <c r="E64" t="s">
-        <v>5</v>
-      </c>
-      <c r="F64" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>22330051920135</v>
-      </c>
-      <c r="B65" t="s">
-        <v>86</v>
-      </c>
-      <c r="C65" t="s">
-        <v>112</v>
-      </c>
-      <c r="D65" t="s">
-        <v>151</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>22330051920244</v>
-      </c>
-      <c r="B66" t="s">
-        <v>86</v>
-      </c>
-      <c r="C66" t="s">
-        <v>117</v>
-      </c>
-      <c r="D66" t="s">
-        <v>152</v>
-      </c>
-      <c r="E66" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>22330051920244</v>
-      </c>
-      <c r="B67" t="s">
-        <v>86</v>
-      </c>
-      <c r="C67" t="s">
-        <v>117</v>
-      </c>
-      <c r="D67" t="s">
-        <v>152</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>22330051920244</v>
-      </c>
-      <c r="B68" t="s">
-        <v>86</v>
-      </c>
-      <c r="C68" t="s">
-        <v>117</v>
-      </c>
-      <c r="D68" t="s">
-        <v>152</v>
-      </c>
-      <c r="E68" t="s">
-        <v>5</v>
-      </c>
-      <c r="F68" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>22330051920244</v>
-      </c>
-      <c r="B69" t="s">
-        <v>86</v>
-      </c>
-      <c r="C69" t="s">
-        <v>117</v>
-      </c>
-      <c r="D69" t="s">
-        <v>152</v>
-      </c>
-      <c r="E69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>22330051920346</v>
-      </c>
-      <c r="B70" t="s">
-        <v>87</v>
-      </c>
-      <c r="C70" t="s">
-        <v>118</v>
-      </c>
-      <c r="D70" t="s">
-        <v>153</v>
-      </c>
-      <c r="E70" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>22330051920346</v>
-      </c>
-      <c r="B71" t="s">
-        <v>87</v>
-      </c>
-      <c r="C71" t="s">
-        <v>118</v>
-      </c>
-      <c r="D71" t="s">
-        <v>153</v>
-      </c>
-      <c r="E71" t="s">
-        <v>6</v>
-      </c>
-      <c r="F71" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>22330051920346</v>
-      </c>
-      <c r="B72" t="s">
-        <v>87</v>
-      </c>
-      <c r="C72" t="s">
-        <v>118</v>
-      </c>
-      <c r="D72" t="s">
-        <v>153</v>
-      </c>
-      <c r="E72" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>22330051920346</v>
-      </c>
-      <c r="B73" t="s">
-        <v>87</v>
-      </c>
-      <c r="C73" t="s">
-        <v>118</v>
-      </c>
-      <c r="D73" t="s">
-        <v>153</v>
-      </c>
-      <c r="E73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>22330051920129</v>
-      </c>
-      <c r="B74" t="s">
-        <v>88</v>
-      </c>
-      <c r="C74" t="s">
-        <v>119</v>
-      </c>
-      <c r="D74" t="s">
-        <v>154</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>22330051920129</v>
-      </c>
-      <c r="B75" t="s">
-        <v>88</v>
-      </c>
-      <c r="C75" t="s">
-        <v>119</v>
-      </c>
-      <c r="D75" t="s">
-        <v>154</v>
-      </c>
-      <c r="E75" t="s">
-        <v>6</v>
-      </c>
-      <c r="F75" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>22330051920129</v>
-      </c>
-      <c r="B76" t="s">
-        <v>88</v>
-      </c>
-      <c r="C76" t="s">
-        <v>119</v>
-      </c>
-      <c r="D76" t="s">
-        <v>154</v>
-      </c>
-      <c r="E76" t="s">
-        <v>5</v>
-      </c>
-      <c r="F76" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>22330051920129</v>
-      </c>
-      <c r="B77" t="s">
-        <v>88</v>
-      </c>
-      <c r="C77" t="s">
-        <v>119</v>
-      </c>
-      <c r="D77" t="s">
-        <v>154</v>
-      </c>
-      <c r="E77" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>22330051920247</v>
-      </c>
-      <c r="B78" t="s">
-        <v>89</v>
-      </c>
-      <c r="C78" t="s">
-        <v>120</v>
-      </c>
-      <c r="D78" t="s">
-        <v>155</v>
-      </c>
-      <c r="E78" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>22330051920247</v>
-      </c>
-      <c r="B79" t="s">
-        <v>89</v>
-      </c>
-      <c r="C79" t="s">
-        <v>120</v>
-      </c>
-      <c r="D79" t="s">
-        <v>155</v>
-      </c>
-      <c r="E79" t="s">
-        <v>6</v>
-      </c>
-      <c r="F79" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>22330051920247</v>
-      </c>
-      <c r="B80" t="s">
-        <v>89</v>
-      </c>
-      <c r="C80" t="s">
-        <v>120</v>
-      </c>
-      <c r="D80" t="s">
-        <v>155</v>
-      </c>
-      <c r="E80" t="s">
-        <v>5</v>
-      </c>
-      <c r="F80" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>22330051920247</v>
-      </c>
-      <c r="B81" t="s">
-        <v>89</v>
-      </c>
-      <c r="C81" t="s">
-        <v>120</v>
-      </c>
-      <c r="D81" t="s">
-        <v>155</v>
-      </c>
-      <c r="E81" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>22330051920347</v>
-      </c>
-      <c r="B82" t="s">
-        <v>90</v>
-      </c>
-      <c r="C82" t="s">
-        <v>121</v>
-      </c>
-      <c r="D82" t="s">
-        <v>156</v>
-      </c>
-      <c r="E82" t="s">
-        <v>9</v>
-      </c>
-      <c r="F82" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>22330051920347</v>
-      </c>
-      <c r="B83" t="s">
-        <v>90</v>
-      </c>
-      <c r="C83" t="s">
-        <v>121</v>
-      </c>
-      <c r="D83" t="s">
-        <v>156</v>
-      </c>
-      <c r="E83" t="s">
-        <v>6</v>
-      </c>
-      <c r="F83" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>22330051920347</v>
-      </c>
-      <c r="B84" t="s">
-        <v>90</v>
-      </c>
-      <c r="C84" t="s">
-        <v>121</v>
-      </c>
-      <c r="D84" t="s">
-        <v>156</v>
-      </c>
-      <c r="E84" t="s">
-        <v>5</v>
-      </c>
-      <c r="F84" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>22330051920347</v>
-      </c>
-      <c r="B85" t="s">
-        <v>90</v>
-      </c>
-      <c r="C85" t="s">
-        <v>121</v>
-      </c>
-      <c r="D85" t="s">
-        <v>156</v>
-      </c>
-      <c r="E85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>22330051920136</v>
-      </c>
-      <c r="B86" t="s">
-        <v>91</v>
-      </c>
-      <c r="C86" t="s">
-        <v>122</v>
-      </c>
-      <c r="D86" t="s">
-        <v>157</v>
-      </c>
-      <c r="E86" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>22330051920136</v>
-      </c>
-      <c r="B87" t="s">
-        <v>91</v>
-      </c>
-      <c r="C87" t="s">
-        <v>122</v>
-      </c>
-      <c r="D87" t="s">
-        <v>157</v>
-      </c>
-      <c r="E87" t="s">
-        <v>6</v>
-      </c>
-      <c r="F87" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>22330051920136</v>
-      </c>
-      <c r="B88" t="s">
-        <v>91</v>
-      </c>
-      <c r="C88" t="s">
-        <v>122</v>
-      </c>
-      <c r="D88" t="s">
-        <v>157</v>
-      </c>
-      <c r="E88" t="s">
-        <v>5</v>
-      </c>
-      <c r="F88" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>22330051920136</v>
-      </c>
-      <c r="B89" t="s">
-        <v>91</v>
-      </c>
-      <c r="C89" t="s">
-        <v>122</v>
-      </c>
-      <c r="D89" t="s">
-        <v>157</v>
-      </c>
-      <c r="E89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>22330051920349</v>
-      </c>
-      <c r="B90" t="s">
-        <v>92</v>
-      </c>
-      <c r="C90" t="s">
-        <v>123</v>
-      </c>
-      <c r="D90" t="s">
-        <v>158</v>
-      </c>
-      <c r="E90" t="s">
-        <v>9</v>
-      </c>
-      <c r="F90" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>22330051920349</v>
-      </c>
-      <c r="B91" t="s">
-        <v>92</v>
-      </c>
-      <c r="C91" t="s">
-        <v>123</v>
-      </c>
-      <c r="D91" t="s">
-        <v>158</v>
-      </c>
-      <c r="E91" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>22330051920349</v>
-      </c>
-      <c r="B92" t="s">
-        <v>92</v>
-      </c>
-      <c r="C92" t="s">
-        <v>123</v>
-      </c>
-      <c r="D92" t="s">
-        <v>158</v>
-      </c>
-      <c r="E92" t="s">
-        <v>5</v>
-      </c>
-      <c r="F92" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>22330051920349</v>
-      </c>
-      <c r="B93" t="s">
-        <v>92</v>
-      </c>
-      <c r="C93" t="s">
-        <v>123</v>
-      </c>
-      <c r="D93" t="s">
-        <v>158</v>
-      </c>
-      <c r="E93" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>22330051920137</v>
-      </c>
-      <c r="B94" t="s">
-        <v>93</v>
-      </c>
-      <c r="C94" t="s">
-        <v>124</v>
-      </c>
-      <c r="D94" t="s">
-        <v>159</v>
-      </c>
-      <c r="E94" t="s">
-        <v>9</v>
-      </c>
-      <c r="F94" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>22330051920137</v>
-      </c>
-      <c r="B95" t="s">
-        <v>93</v>
-      </c>
-      <c r="C95" t="s">
-        <v>124</v>
-      </c>
-      <c r="D95" t="s">
-        <v>159</v>
-      </c>
-      <c r="E95" t="s">
-        <v>6</v>
-      </c>
-      <c r="F95" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>22330051920137</v>
-      </c>
-      <c r="B96" t="s">
-        <v>93</v>
-      </c>
-      <c r="C96" t="s">
-        <v>124</v>
-      </c>
-      <c r="D96" t="s">
-        <v>159</v>
-      </c>
-      <c r="E96" t="s">
-        <v>5</v>
-      </c>
-      <c r="F96" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>22330051920137</v>
-      </c>
-      <c r="B97" t="s">
-        <v>93</v>
-      </c>
-      <c r="C97" t="s">
-        <v>124</v>
-      </c>
-      <c r="D97" t="s">
-        <v>159</v>
-      </c>
-      <c r="E97" t="s">
-        <v>8</v>
-      </c>
-      <c r="F97" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>22330051920350</v>
-      </c>
-      <c r="B98" t="s">
-        <v>94</v>
-      </c>
-      <c r="C98" t="s">
-        <v>125</v>
-      </c>
-      <c r="D98" t="s">
-        <v>160</v>
-      </c>
-      <c r="E98" t="s">
-        <v>9</v>
-      </c>
-      <c r="F98" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>22330051920350</v>
-      </c>
-      <c r="B99" t="s">
-        <v>94</v>
-      </c>
-      <c r="C99" t="s">
-        <v>125</v>
-      </c>
-      <c r="D99" t="s">
-        <v>160</v>
-      </c>
-      <c r="E99" t="s">
-        <v>6</v>
-      </c>
-      <c r="F99" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>22330051920350</v>
-      </c>
-      <c r="B100" t="s">
-        <v>94</v>
-      </c>
-      <c r="C100" t="s">
-        <v>125</v>
-      </c>
-      <c r="D100" t="s">
-        <v>160</v>
-      </c>
-      <c r="E100" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>22330051920350</v>
-      </c>
-      <c r="B101" t="s">
-        <v>94</v>
-      </c>
-      <c r="C101" t="s">
-        <v>125</v>
-      </c>
-      <c r="D101" t="s">
-        <v>160</v>
-      </c>
-      <c r="E101" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>22330051920138</v>
-      </c>
-      <c r="B102" t="s">
-        <v>95</v>
-      </c>
-      <c r="C102" t="s">
-        <v>117</v>
-      </c>
-      <c r="D102" t="s">
-        <v>161</v>
-      </c>
-      <c r="E102" t="s">
-        <v>9</v>
-      </c>
-      <c r="F102" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>22330051920138</v>
-      </c>
-      <c r="B103" t="s">
-        <v>95</v>
-      </c>
-      <c r="C103" t="s">
-        <v>117</v>
-      </c>
-      <c r="D103" t="s">
-        <v>161</v>
-      </c>
-      <c r="E103" t="s">
-        <v>6</v>
-      </c>
-      <c r="F103" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>22330051920138</v>
-      </c>
-      <c r="B104" t="s">
-        <v>95</v>
-      </c>
-      <c r="C104" t="s">
-        <v>117</v>
-      </c>
-      <c r="D104" t="s">
-        <v>161</v>
-      </c>
-      <c r="E104" t="s">
-        <v>5</v>
-      </c>
-      <c r="F104" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>22330051920138</v>
-      </c>
-      <c r="B105" t="s">
-        <v>95</v>
-      </c>
-      <c r="C105" t="s">
-        <v>117</v>
-      </c>
-      <c r="D105" t="s">
-        <v>161</v>
-      </c>
-      <c r="E105" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>22330051920110</v>
-      </c>
-      <c r="B106" t="s">
-        <v>96</v>
-      </c>
-      <c r="C106" t="s">
-        <v>120</v>
-      </c>
-      <c r="D106" t="s">
-        <v>162</v>
-      </c>
-      <c r="E106" t="s">
-        <v>9</v>
-      </c>
-      <c r="F106" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>22330051920110</v>
-      </c>
-      <c r="B107" t="s">
-        <v>96</v>
-      </c>
-      <c r="C107" t="s">
-        <v>120</v>
-      </c>
-      <c r="D107" t="s">
-        <v>162</v>
-      </c>
-      <c r="E107" t="s">
-        <v>6</v>
-      </c>
-      <c r="F107" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>22330051920110</v>
-      </c>
-      <c r="B108" t="s">
-        <v>96</v>
-      </c>
-      <c r="C108" t="s">
-        <v>120</v>
-      </c>
-      <c r="D108" t="s">
-        <v>162</v>
-      </c>
-      <c r="E108" t="s">
-        <v>5</v>
-      </c>
-      <c r="F108" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>22330051920110</v>
-      </c>
-      <c r="B109" t="s">
-        <v>96</v>
-      </c>
-      <c r="C109" t="s">
-        <v>120</v>
-      </c>
-      <c r="D109" t="s">
-        <v>162</v>
-      </c>
-      <c r="E109" t="s">
-        <v>8</v>
-      </c>
-      <c r="F109" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>22330051920140</v>
-      </c>
-      <c r="B110" t="s">
-        <v>97</v>
-      </c>
-      <c r="C110" t="s">
-        <v>126</v>
-      </c>
-      <c r="D110" t="s">
-        <v>163</v>
-      </c>
-      <c r="E110" t="s">
-        <v>9</v>
-      </c>
-      <c r="F110" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>22330051920140</v>
-      </c>
-      <c r="B111" t="s">
-        <v>97</v>
-      </c>
-      <c r="C111" t="s">
-        <v>126</v>
-      </c>
-      <c r="D111" t="s">
-        <v>163</v>
-      </c>
-      <c r="E111" t="s">
-        <v>6</v>
-      </c>
-      <c r="F111" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>22330051920140</v>
-      </c>
-      <c r="B112" t="s">
-        <v>97</v>
-      </c>
-      <c r="C112" t="s">
-        <v>126</v>
-      </c>
-      <c r="D112" t="s">
-        <v>163</v>
-      </c>
-      <c r="E112" t="s">
-        <v>5</v>
-      </c>
-      <c r="F112" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>22330051920140</v>
-      </c>
-      <c r="B113" t="s">
-        <v>97</v>
-      </c>
-      <c r="C113" t="s">
-        <v>126</v>
-      </c>
-      <c r="D113" t="s">
-        <v>163</v>
-      </c>
-      <c r="E113" t="s">
-        <v>8</v>
-      </c>
-      <c r="F113" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>22330051920352</v>
-      </c>
-      <c r="B114" t="s">
-        <v>98</v>
-      </c>
-      <c r="C114" t="s">
-        <v>110</v>
-      </c>
-      <c r="D114" t="s">
-        <v>164</v>
-      </c>
-      <c r="E114" t="s">
-        <v>9</v>
-      </c>
-      <c r="F114" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>22330051920352</v>
-      </c>
-      <c r="B115" t="s">
-        <v>98</v>
-      </c>
-      <c r="C115" t="s">
-        <v>110</v>
-      </c>
-      <c r="D115" t="s">
-        <v>164</v>
-      </c>
-      <c r="E115" t="s">
-        <v>6</v>
-      </c>
-      <c r="F115" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>22330051920352</v>
-      </c>
-      <c r="B116" t="s">
-        <v>98</v>
-      </c>
-      <c r="C116" t="s">
-        <v>110</v>
-      </c>
-      <c r="D116" t="s">
-        <v>164</v>
-      </c>
-      <c r="E116" t="s">
-        <v>5</v>
-      </c>
-      <c r="F116" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>22330051920352</v>
-      </c>
-      <c r="B117" t="s">
-        <v>98</v>
-      </c>
-      <c r="C117" t="s">
-        <v>110</v>
-      </c>
-      <c r="D117" t="s">
-        <v>164</v>
-      </c>
-      <c r="E117" t="s">
-        <v>8</v>
-      </c>
-      <c r="F117" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>22330051920252</v>
-      </c>
-      <c r="B118" t="s">
-        <v>99</v>
-      </c>
-      <c r="C118" t="s">
-        <v>127</v>
-      </c>
-      <c r="D118" t="s">
-        <v>165</v>
-      </c>
-      <c r="E118" t="s">
-        <v>9</v>
-      </c>
-      <c r="F118" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>22330051920252</v>
-      </c>
-      <c r="B119" t="s">
-        <v>99</v>
-      </c>
-      <c r="C119" t="s">
-        <v>127</v>
-      </c>
-      <c r="D119" t="s">
-        <v>165</v>
-      </c>
-      <c r="E119" t="s">
-        <v>6</v>
-      </c>
-      <c r="F119" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>22330051920252</v>
-      </c>
-      <c r="B120" t="s">
-        <v>99</v>
-      </c>
-      <c r="C120" t="s">
-        <v>127</v>
-      </c>
-      <c r="D120" t="s">
-        <v>165</v>
-      </c>
-      <c r="E120" t="s">
-        <v>5</v>
-      </c>
-      <c r="F120" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>22330051920252</v>
-      </c>
-      <c r="B121" t="s">
-        <v>99</v>
-      </c>
-      <c r="C121" t="s">
-        <v>127</v>
-      </c>
-      <c r="D121" t="s">
-        <v>165</v>
-      </c>
-      <c r="E121" t="s">
-        <v>8</v>
-      </c>
-      <c r="F121" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>22330051920142</v>
-      </c>
-      <c r="B122" t="s">
-        <v>100</v>
-      </c>
-      <c r="C122" t="s">
-        <v>128</v>
-      </c>
-      <c r="D122" t="s">
-        <v>166</v>
-      </c>
-      <c r="E122" t="s">
-        <v>9</v>
-      </c>
-      <c r="F122" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>22330051920142</v>
-      </c>
-      <c r="B123" t="s">
-        <v>100</v>
-      </c>
-      <c r="C123" t="s">
-        <v>128</v>
-      </c>
-      <c r="D123" t="s">
-        <v>166</v>
-      </c>
-      <c r="E123" t="s">
-        <v>6</v>
-      </c>
-      <c r="F123" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>22330051920142</v>
-      </c>
-      <c r="B124" t="s">
-        <v>100</v>
-      </c>
-      <c r="C124" t="s">
-        <v>128</v>
-      </c>
-      <c r="D124" t="s">
-        <v>166</v>
-      </c>
-      <c r="E124" t="s">
-        <v>5</v>
-      </c>
-      <c r="F124" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>22330051920142</v>
-      </c>
-      <c r="B125" t="s">
-        <v>100</v>
-      </c>
-      <c r="C125" t="s">
-        <v>128</v>
-      </c>
-      <c r="D125" t="s">
-        <v>166</v>
-      </c>
-      <c r="E125" t="s">
-        <v>8</v>
-      </c>
-      <c r="F125" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>22330051920353</v>
-      </c>
-      <c r="B126" t="s">
-        <v>101</v>
-      </c>
-      <c r="C126" t="s">
-        <v>108</v>
-      </c>
-      <c r="D126" t="s">
-        <v>167</v>
-      </c>
-      <c r="E126" t="s">
-        <v>9</v>
-      </c>
-      <c r="F126" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>22330051920353</v>
-      </c>
-      <c r="B127" t="s">
-        <v>101</v>
-      </c>
-      <c r="C127" t="s">
-        <v>108</v>
-      </c>
-      <c r="D127" t="s">
-        <v>167</v>
-      </c>
-      <c r="E127" t="s">
-        <v>6</v>
-      </c>
-      <c r="F127" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>22330051920353</v>
-      </c>
-      <c r="B128" t="s">
-        <v>101</v>
-      </c>
-      <c r="C128" t="s">
-        <v>108</v>
-      </c>
-      <c r="D128" t="s">
-        <v>167</v>
-      </c>
-      <c r="E128" t="s">
-        <v>5</v>
-      </c>
-      <c r="F128" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>22330051920353</v>
-      </c>
-      <c r="B129" t="s">
-        <v>101</v>
-      </c>
-      <c r="C129" t="s">
-        <v>108</v>
-      </c>
-      <c r="D129" t="s">
-        <v>167</v>
-      </c>
-      <c r="E129" t="s">
-        <v>8</v>
-      </c>
-      <c r="F129" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>22330051920354</v>
-      </c>
-      <c r="B130" t="s">
-        <v>102</v>
-      </c>
-      <c r="C130" t="s">
-        <v>129</v>
-      </c>
-      <c r="D130" t="s">
-        <v>168</v>
-      </c>
-      <c r="E130" t="s">
-        <v>9</v>
-      </c>
-      <c r="F130" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
-        <v>22330051920354</v>
-      </c>
-      <c r="B131" t="s">
-        <v>102</v>
-      </c>
-      <c r="C131" t="s">
-        <v>129</v>
-      </c>
-      <c r="D131" t="s">
-        <v>168</v>
-      </c>
-      <c r="E131" t="s">
-        <v>6</v>
-      </c>
-      <c r="F131" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132">
-        <v>22330051920354</v>
-      </c>
-      <c r="B132" t="s">
-        <v>102</v>
-      </c>
-      <c r="C132" t="s">
-        <v>129</v>
-      </c>
-      <c r="D132" t="s">
-        <v>168</v>
-      </c>
-      <c r="E132" t="s">
-        <v>5</v>
-      </c>
-      <c r="F132" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>22330051920354</v>
-      </c>
-      <c r="B133" t="s">
-        <v>102</v>
-      </c>
-      <c r="C133" t="s">
-        <v>129</v>
-      </c>
-      <c r="D133" t="s">
-        <v>168</v>
-      </c>
-      <c r="E133" t="s">
-        <v>8</v>
-      </c>
-      <c r="F133" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134">
-        <v>22330051920143</v>
-      </c>
-      <c r="B134" t="s">
-        <v>103</v>
-      </c>
-      <c r="C134" t="s">
-        <v>110</v>
-      </c>
-      <c r="D134" t="s">
-        <v>169</v>
-      </c>
-      <c r="E134" t="s">
-        <v>9</v>
-      </c>
-      <c r="F134" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135">
-        <v>22330051920143</v>
-      </c>
-      <c r="B135" t="s">
-        <v>103</v>
-      </c>
-      <c r="C135" t="s">
-        <v>110</v>
-      </c>
-      <c r="D135" t="s">
-        <v>169</v>
-      </c>
-      <c r="E135" t="s">
-        <v>6</v>
-      </c>
-      <c r="F135" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136">
-        <v>22330051920143</v>
-      </c>
-      <c r="B136" t="s">
-        <v>103</v>
-      </c>
-      <c r="C136" t="s">
-        <v>110</v>
-      </c>
-      <c r="D136" t="s">
-        <v>169</v>
-      </c>
-      <c r="E136" t="s">
-        <v>5</v>
-      </c>
-      <c r="F136" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137">
-        <v>22330051920143</v>
-      </c>
-      <c r="B137" t="s">
-        <v>103</v>
-      </c>
-      <c r="C137" t="s">
-        <v>110</v>
-      </c>
-      <c r="D137" t="s">
-        <v>169</v>
-      </c>
-      <c r="E137" t="s">
-        <v>8</v>
-      </c>
-      <c r="F137" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138">
-        <v>22330051920144</v>
-      </c>
-      <c r="B138" t="s">
-        <v>104</v>
-      </c>
-      <c r="C138" t="s">
-        <v>130</v>
-      </c>
-      <c r="D138" t="s">
-        <v>170</v>
-      </c>
-      <c r="E138" t="s">
-        <v>9</v>
-      </c>
-      <c r="F138" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139">
-        <v>22330051920144</v>
-      </c>
-      <c r="B139" t="s">
-        <v>104</v>
-      </c>
-      <c r="C139" t="s">
-        <v>130</v>
-      </c>
-      <c r="D139" t="s">
-        <v>170</v>
-      </c>
-      <c r="E139" t="s">
-        <v>6</v>
-      </c>
-      <c r="F139" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140">
-        <v>22330051920144</v>
-      </c>
-      <c r="B140" t="s">
-        <v>104</v>
-      </c>
-      <c r="C140" t="s">
-        <v>130</v>
-      </c>
-      <c r="D140" t="s">
-        <v>170</v>
-      </c>
-      <c r="E140" t="s">
-        <v>5</v>
-      </c>
-      <c r="F140" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141">
-        <v>22330051920144</v>
-      </c>
-      <c r="B141" t="s">
-        <v>104</v>
-      </c>
-      <c r="C141" t="s">
-        <v>130</v>
-      </c>
-      <c r="D141" t="s">
-        <v>170</v>
-      </c>
-      <c r="E141" t="s">
-        <v>8</v>
-      </c>
-      <c r="F141" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142">
-        <v>22330051920145</v>
-      </c>
-      <c r="B142" t="s">
-        <v>104</v>
-      </c>
-      <c r="C142" t="s">
-        <v>131</v>
-      </c>
-      <c r="D142" t="s">
-        <v>171</v>
-      </c>
-      <c r="E142" t="s">
-        <v>9</v>
-      </c>
-      <c r="F142" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143">
-        <v>22330051920145</v>
-      </c>
-      <c r="B143" t="s">
-        <v>104</v>
-      </c>
-      <c r="C143" t="s">
-        <v>131</v>
-      </c>
-      <c r="D143" t="s">
-        <v>171</v>
-      </c>
-      <c r="E143" t="s">
-        <v>6</v>
-      </c>
-      <c r="F143" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144">
-        <v>22330051920145</v>
-      </c>
-      <c r="B144" t="s">
-        <v>104</v>
-      </c>
-      <c r="C144" t="s">
-        <v>131</v>
-      </c>
-      <c r="D144" t="s">
-        <v>171</v>
-      </c>
-      <c r="E144" t="s">
-        <v>5</v>
-      </c>
-      <c r="F144" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145">
-        <v>22330051920145</v>
-      </c>
-      <c r="B145" t="s">
-        <v>104</v>
-      </c>
-      <c r="C145" t="s">
-        <v>131</v>
-      </c>
-      <c r="D145" t="s">
-        <v>171</v>
-      </c>
-      <c r="E145" t="s">
-        <v>8</v>
-      </c>
-      <c r="F145" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146">
-        <v>22330051920146</v>
-      </c>
-      <c r="B146" t="s">
-        <v>105</v>
-      </c>
-      <c r="C146" t="s">
-        <v>81</v>
-      </c>
-      <c r="D146" t="s">
-        <v>172</v>
-      </c>
-      <c r="E146" t="s">
-        <v>9</v>
-      </c>
-      <c r="F146" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147">
-        <v>22330051920146</v>
-      </c>
-      <c r="B147" t="s">
-        <v>105</v>
-      </c>
-      <c r="C147" t="s">
-        <v>81</v>
-      </c>
-      <c r="D147" t="s">
-        <v>172</v>
-      </c>
-      <c r="E147" t="s">
-        <v>6</v>
-      </c>
-      <c r="F147" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148">
-        <v>22330051920146</v>
-      </c>
-      <c r="B148" t="s">
-        <v>105</v>
-      </c>
-      <c r="C148" t="s">
-        <v>81</v>
-      </c>
-      <c r="D148" t="s">
-        <v>172</v>
-      </c>
-      <c r="E148" t="s">
-        <v>5</v>
-      </c>
-      <c r="F148" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149">
-        <v>22330051920146</v>
-      </c>
-      <c r="B149" t="s">
-        <v>105</v>
-      </c>
-      <c r="C149" t="s">
-        <v>81</v>
-      </c>
-      <c r="D149" t="s">
-        <v>172</v>
-      </c>
-      <c r="E149" t="s">
-        <v>8</v>
-      </c>
-      <c r="F149" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150">
-        <v>22330051920258</v>
-      </c>
-      <c r="B150" t="s">
-        <v>106</v>
-      </c>
-      <c r="C150" t="s">
-        <v>132</v>
-      </c>
-      <c r="D150" t="s">
-        <v>173</v>
-      </c>
-      <c r="E150" t="s">
-        <v>9</v>
-      </c>
-      <c r="F150" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151">
-        <v>22330051920258</v>
-      </c>
-      <c r="B151" t="s">
-        <v>106</v>
-      </c>
-      <c r="C151" t="s">
-        <v>132</v>
-      </c>
-      <c r="D151" t="s">
-        <v>173</v>
-      </c>
-      <c r="E151" t="s">
-        <v>6</v>
-      </c>
-      <c r="F151" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152">
-        <v>22330051920258</v>
-      </c>
-      <c r="B152" t="s">
-        <v>106</v>
-      </c>
-      <c r="C152" t="s">
-        <v>132</v>
-      </c>
-      <c r="D152" t="s">
-        <v>173</v>
-      </c>
-      <c r="E152" t="s">
-        <v>5</v>
-      </c>
-      <c r="F152" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153">
-        <v>22330051920258</v>
-      </c>
-      <c r="B153" t="s">
-        <v>106</v>
-      </c>
-      <c r="C153" t="s">
-        <v>132</v>
-      </c>
-      <c r="D153" t="s">
-        <v>173</v>
-      </c>
-      <c r="E153" t="s">
-        <v>8</v>
-      </c>
-      <c r="F153" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154">
-        <v>22330051920355</v>
-      </c>
-      <c r="B154" t="s">
-        <v>107</v>
-      </c>
-      <c r="C154" t="s">
-        <v>133</v>
-      </c>
-      <c r="D154" t="s">
-        <v>174</v>
-      </c>
-      <c r="E154" t="s">
-        <v>9</v>
-      </c>
-      <c r="F154" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155">
-        <v>22330051920355</v>
-      </c>
-      <c r="B155" t="s">
-        <v>107</v>
-      </c>
-      <c r="C155" t="s">
-        <v>133</v>
-      </c>
-      <c r="D155" t="s">
-        <v>174</v>
-      </c>
-      <c r="E155" t="s">
-        <v>6</v>
-      </c>
-      <c r="F155" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156">
-        <v>22330051920355</v>
-      </c>
-      <c r="B156" t="s">
-        <v>107</v>
-      </c>
-      <c r="C156" t="s">
-        <v>133</v>
-      </c>
-      <c r="D156" t="s">
-        <v>174</v>
-      </c>
-      <c r="E156" t="s">
-        <v>5</v>
-      </c>
-      <c r="F156" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157">
-        <v>22330051920355</v>
-      </c>
-      <c r="B157" t="s">
-        <v>107</v>
-      </c>
-      <c r="C157" t="s">
-        <v>133</v>
-      </c>
-      <c r="D157" t="s">
-        <v>174</v>
-      </c>
-      <c r="E157" t="s">
-        <v>8</v>
-      </c>
-      <c r="F157" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158">
-        <v>22330051920147</v>
-      </c>
-      <c r="B158" t="s">
-        <v>108</v>
-      </c>
-      <c r="C158" t="s">
-        <v>134</v>
-      </c>
-      <c r="D158" t="s">
-        <v>175</v>
-      </c>
-      <c r="E158" t="s">
-        <v>9</v>
-      </c>
-      <c r="F158" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159">
-        <v>22330051920147</v>
-      </c>
-      <c r="B159" t="s">
-        <v>108</v>
-      </c>
-      <c r="C159" t="s">
-        <v>134</v>
-      </c>
-      <c r="D159" t="s">
-        <v>175</v>
-      </c>
-      <c r="E159" t="s">
-        <v>6</v>
-      </c>
-      <c r="F159" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160">
-        <v>22330051920147</v>
-      </c>
-      <c r="B160" t="s">
-        <v>108</v>
-      </c>
-      <c r="C160" t="s">
-        <v>134</v>
-      </c>
-      <c r="D160" t="s">
-        <v>175</v>
-      </c>
-      <c r="E160" t="s">
-        <v>5</v>
-      </c>
-      <c r="F160" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161">
-        <v>22330051920147</v>
-      </c>
-      <c r="B161" t="s">
-        <v>108</v>
-      </c>
-      <c r="C161" t="s">
-        <v>134</v>
-      </c>
-      <c r="D161" t="s">
-        <v>175</v>
-      </c>
-      <c r="E161" t="s">
-        <v>8</v>
-      </c>
-      <c r="F161" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="A162">
-        <v>22330051920148</v>
-      </c>
-      <c r="B162" t="s">
-        <v>109</v>
-      </c>
-      <c r="C162" t="s">
-        <v>135</v>
-      </c>
-      <c r="D162" t="s">
-        <v>176</v>
-      </c>
-      <c r="E162" t="s">
-        <v>9</v>
-      </c>
-      <c r="F162" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="A163">
-        <v>22330051920148</v>
-      </c>
-      <c r="B163" t="s">
-        <v>109</v>
-      </c>
-      <c r="C163" t="s">
-        <v>135</v>
-      </c>
-      <c r="D163" t="s">
-        <v>176</v>
-      </c>
-      <c r="E163" t="s">
-        <v>6</v>
-      </c>
-      <c r="F163" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="A164">
-        <v>22330051920148</v>
-      </c>
-      <c r="B164" t="s">
-        <v>109</v>
-      </c>
-      <c r="C164" t="s">
-        <v>135</v>
-      </c>
-      <c r="D164" t="s">
-        <v>176</v>
-      </c>
-      <c r="E164" t="s">
-        <v>5</v>
-      </c>
-      <c r="F164" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165">
-        <v>22330051920148</v>
-      </c>
-      <c r="B165" t="s">
-        <v>109</v>
-      </c>
-      <c r="C165" t="s">
-        <v>135</v>
-      </c>
-      <c r="D165" t="s">
-        <v>176</v>
-      </c>
-      <c r="E165" t="s">
-        <v>8</v>
-      </c>
-      <c r="F165" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -10305,7 +7854,7 @@
         <v>136</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -10322,7 +7871,7 @@
         <v>137</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -10339,7 +7888,7 @@
         <v>138</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -10356,7 +7905,7 @@
         <v>139</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -10373,7 +7922,7 @@
         <v>140</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -10390,7 +7939,7 @@
         <v>141</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -10407,7 +7956,7 @@
         <v>142</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -10424,7 +7973,7 @@
         <v>143</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -10441,7 +7990,7 @@
         <v>144</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -10458,7 +8007,7 @@
         <v>145</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -10475,7 +8024,7 @@
         <v>146</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -10492,7 +8041,7 @@
         <v>147</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -10509,7 +8058,7 @@
         <v>148</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -10526,7 +8075,7 @@
         <v>149</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -10543,7 +8092,7 @@
         <v>150</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -10560,7 +8109,7 @@
         <v>151</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -10577,7 +8126,7 @@
         <v>152</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -10594,7 +8143,7 @@
         <v>153</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -10611,7 +8160,7 @@
         <v>154</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -10628,7 +8177,7 @@
         <v>155</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -10645,7 +8194,7 @@
         <v>156</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -10662,7 +8211,7 @@
         <v>157</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -10679,7 +8228,7 @@
         <v>158</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -10696,7 +8245,7 @@
         <v>159</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -10713,7 +8262,7 @@
         <v>160</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -10730,7 +8279,7 @@
         <v>161</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -10747,7 +8296,7 @@
         <v>162</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -10764,7 +8313,7 @@
         <v>163</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -10781,7 +8330,7 @@
         <v>164</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -10798,7 +8347,7 @@
         <v>165</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -10815,7 +8364,7 @@
         <v>166</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -10832,7 +8381,7 @@
         <v>167</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -10849,7 +8398,7 @@
         <v>168</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -10866,7 +8415,7 @@
         <v>169</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -10883,7 +8432,7 @@
         <v>170</v>
       </c>
       <c r="E36">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -10900,7 +8449,7 @@
         <v>171</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -10917,7 +8466,7 @@
         <v>172</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -10934,7 +8483,7 @@
         <v>173</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -10951,7 +8500,7 @@
         <v>174</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -10968,7 +8517,7 @@
         <v>175</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -10985,7 +8534,7 @@
         <v>176</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -10995,7 +8544,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -11025,6 +8574,696 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920343</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920343</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920344</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920344</v>
+      </c>
+      <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920130</v>
+      </c>
+      <c r="B6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920130</v>
+      </c>
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920124</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920125</v>
+      </c>
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920127</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920345</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" t="s">
+        <v>144</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920128</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920131</v>
+      </c>
+      <c r="B13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920133</v>
+      </c>
+      <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" t="s">
+        <v>149</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920134</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920135</v>
+      </c>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920129</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" t="s">
+        <v>154</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920347</v>
+      </c>
+      <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" t="s">
+        <v>156</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920349</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920137</v>
+      </c>
+      <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" t="s">
+        <v>159</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920350</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920138</v>
+      </c>
+      <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" t="s">
+        <v>161</v>
+      </c>
+      <c r="E22" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920110</v>
+      </c>
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" t="s">
+        <v>162</v>
+      </c>
+      <c r="E23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920140</v>
+      </c>
+      <c r="B24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>22330051920252</v>
+      </c>
+      <c r="B25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" t="s">
+        <v>127</v>
+      </c>
+      <c r="D25" t="s">
+        <v>165</v>
+      </c>
+      <c r="E25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22330051920142</v>
+      </c>
+      <c r="B26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" t="s">
+        <v>128</v>
+      </c>
+      <c r="D26" t="s">
+        <v>166</v>
+      </c>
+      <c r="E26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>22330051920143</v>
+      </c>
+      <c r="B27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" t="s">
+        <v>169</v>
+      </c>
+      <c r="E27" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>22330051920146</v>
+      </c>
+      <c r="B28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>22330051920355</v>
+      </c>
+      <c r="B29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>22330051920147</v>
+      </c>
+      <c r="B30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" t="s">
+        <v>175</v>
+      </c>
+      <c r="E30" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" t="s">
+        <v>65</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>22330051920148</v>
+      </c>
+      <c r="B31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" t="s">
+        <v>176</v>
+      </c>
+      <c r="E31" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/2BLCM - Estadisticos 20222.xlsx
+++ b/grupos/2BLCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="177">
   <si>
     <t>Materia</t>
   </si>
@@ -1038,7 +1038,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -1092,7 +1092,7 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -1115,7 +1115,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -1169,7 +1169,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -1192,7 +1192,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1246,7 +1246,7 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1269,7 +1269,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1323,7 +1323,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -1346,7 +1346,7 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -1400,7 +1400,7 @@
         <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -1423,7 +1423,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -1477,7 +1477,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -1500,7 +1500,7 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1554,7 +1554,7 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1577,7 +1577,7 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -1631,7 +1631,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -1654,7 +1654,7 @@
         <v>10</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -1708,7 +1708,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1731,7 +1731,7 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>8</v>
@@ -1785,7 +1785,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -1808,7 +1808,7 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -1862,7 +1862,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>6</v>
@@ -1885,7 +1885,7 @@
         <v>5</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>6</v>
@@ -1939,7 +1939,7 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1962,7 +1962,7 @@
         <v>7</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>6</v>
@@ -2016,7 +2016,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>6</v>
@@ -2039,7 +2039,7 @@
         <v>6</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -2093,7 +2093,7 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -2116,7 +2116,7 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D18">
         <v>7</v>
@@ -2170,7 +2170,7 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -2193,7 +2193,7 @@
         <v>10</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>10</v>
@@ -2247,7 +2247,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>10</v>
@@ -2270,7 +2270,7 @@
         <v>7</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -2324,7 +2324,7 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2347,7 +2347,7 @@
         <v>5</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -2401,7 +2401,7 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -2424,7 +2424,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>5</v>
@@ -2478,7 +2478,7 @@
         <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2501,7 +2501,7 @@
         <v>5</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -2555,7 +2555,7 @@
         <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2578,7 +2578,7 @@
         <v>9</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D24">
         <v>10</v>
@@ -2632,7 +2632,7 @@
         <v>9</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>10</v>
@@ -2655,7 +2655,7 @@
         <v>5</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>5</v>
@@ -2709,7 +2709,7 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -2732,7 +2732,7 @@
         <v>7</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D26">
         <v>6</v>
@@ -2786,7 +2786,7 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>6</v>
@@ -2809,7 +2809,7 @@
         <v>8</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D27">
         <v>8</v>
@@ -2863,7 +2863,7 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -2886,7 +2886,7 @@
         <v>9</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D28">
         <v>8</v>
@@ -2940,7 +2940,7 @@
         <v>9</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -2963,7 +2963,7 @@
         <v>7</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <v>6</v>
@@ -3017,7 +3017,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>6</v>
@@ -3040,7 +3040,7 @@
         <v>8</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D30">
         <v>6</v>
@@ -3094,7 +3094,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>6</v>
@@ -3117,7 +3117,7 @@
         <v>5</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -3171,7 +3171,7 @@
         <v>5</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
         <v>5</v>
@@ -3194,7 +3194,7 @@
         <v>8</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D32">
         <v>10</v>
@@ -3248,7 +3248,7 @@
         <v>8</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3271,7 +3271,7 @@
         <v>7</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D33">
         <v>10</v>
@@ -3325,7 +3325,7 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -3348,7 +3348,7 @@
         <v>7</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D34">
         <v>6</v>
@@ -3402,7 +3402,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>6</v>
@@ -3425,7 +3425,7 @@
         <v>5</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D35">
         <v>5</v>
@@ -3479,7 +3479,7 @@
         <v>5</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>5</v>
@@ -3502,7 +3502,7 @@
         <v>6</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -3556,7 +3556,7 @@
         <v>6</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -3579,7 +3579,7 @@
         <v>7</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D37">
         <v>6</v>
@@ -3633,7 +3633,7 @@
         <v>7</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V37">
         <v>6</v>
@@ -3656,7 +3656,7 @@
         <v>8</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D38">
         <v>8</v>
@@ -3710,7 +3710,7 @@
         <v>8</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
         <v>8</v>
@@ -3733,7 +3733,7 @@
         <v>7</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -3787,7 +3787,7 @@
         <v>7</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V39">
         <v>5</v>
@@ -3810,7 +3810,7 @@
         <v>5</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D40">
         <v>5</v>
@@ -3864,7 +3864,7 @@
         <v>5</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V40">
         <v>5</v>
@@ -3887,7 +3887,7 @@
         <v>7</v>
       </c>
       <c r="C41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D41">
         <v>7</v>
@@ -3941,7 +3941,7 @@
         <v>7</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V41">
         <v>7</v>
@@ -3964,7 +3964,7 @@
         <v>7</v>
       </c>
       <c r="C42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D42">
         <v>8</v>
@@ -4018,7 +4018,7 @@
         <v>7</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V42">
         <v>8</v>
@@ -4041,7 +4041,7 @@
         <v>9</v>
       </c>
       <c r="C43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D43">
         <v>9</v>
@@ -4095,7 +4095,7 @@
         <v>9</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V43">
         <v>9</v>
@@ -4118,7 +4118,7 @@
         <v>6</v>
       </c>
       <c r="C44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D44">
         <v>7</v>
@@ -4172,7 +4172,7 @@
         <v>6</v>
       </c>
       <c r="U44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V44">
         <v>7</v>
@@ -4305,7 +4305,7 @@
         <v>120</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>120</v>
@@ -4364,7 +4364,7 @@
         <v>115</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>115</v>
@@ -4423,7 +4423,7 @@
         <v>105</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>70</v>
@@ -4482,7 +4482,7 @@
         <v>120</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>110</v>
@@ -4541,7 +4541,7 @@
         <v>120</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>120</v>
@@ -4600,7 +4600,7 @@
         <v>110</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>110</v>
@@ -4659,7 +4659,7 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>70</v>
@@ -4718,7 +4718,7 @@
         <v>115</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>120</v>
@@ -4777,7 +4777,7 @@
         <v>120</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>120</v>
@@ -4836,7 +4836,7 @@
         <v>120</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>120</v>
@@ -4895,7 +4895,7 @@
         <v>120</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>120</v>
@@ -4954,7 +4954,7 @@
         <v>105</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>120</v>
@@ -5013,7 +5013,7 @@
         <v>120</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>120</v>
@@ -5072,7 +5072,7 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>90</v>
@@ -5131,7 +5131,7 @@
         <v>115</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>100</v>
@@ -5190,7 +5190,7 @@
         <v>120</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>120</v>
@@ -5249,7 +5249,7 @@
         <v>120</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>120</v>
@@ -5308,7 +5308,7 @@
         <v>85</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="D21">
         <v>110</v>
@@ -5367,7 +5367,7 @@
         <v>120</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>60</v>
@@ -5426,7 +5426,7 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>110</v>
@@ -5485,7 +5485,7 @@
         <v>120</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>120</v>
@@ -5544,7 +5544,7 @@
         <v>110</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>95</v>
@@ -5603,7 +5603,7 @@
         <v>120</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>120</v>
@@ -5662,7 +5662,7 @@
         <v>120</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>120</v>
@@ -5721,7 +5721,7 @@
         <v>115</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>120</v>
@@ -5780,7 +5780,7 @@
         <v>115</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>120</v>
@@ -5839,7 +5839,7 @@
         <v>120</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>120</v>
@@ -5898,7 +5898,7 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="D31">
         <v>100</v>
@@ -5957,7 +5957,7 @@
         <v>120</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>120</v>
@@ -6016,7 +6016,7 @@
         <v>120</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>120</v>
@@ -6075,7 +6075,7 @@
         <v>105</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>120</v>
@@ -6134,7 +6134,7 @@
         <v>120</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>120</v>
@@ -6193,7 +6193,7 @@
         <v>120</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>120</v>
@@ -6252,7 +6252,7 @@
         <v>120</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>120</v>
@@ -6311,7 +6311,7 @@
         <v>120</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D38">
         <v>110</v>
@@ -6370,7 +6370,7 @@
         <v>90</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>120</v>
@@ -6429,7 +6429,7 @@
         <v>110</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D40">
         <v>110</v>
@@ -6488,7 +6488,7 @@
         <v>120</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D41">
         <v>120</v>
@@ -6547,7 +6547,7 @@
         <v>120</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D42">
         <v>120</v>
@@ -6606,7 +6606,7 @@
         <v>120</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D43">
         <v>120</v>
@@ -6665,7 +6665,7 @@
         <v>115</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D44">
         <v>120</v>
@@ -6768,7 +6768,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -6777,27 +6777,30 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>34.15</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -6806,19 +6809,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>65.84999999999999</v>
+        <v>73.17</v>
       </c>
       <c r="G3">
-        <v>34.15</v>
+        <v>26.83</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6829,7 +6832,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -6838,19 +6841,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>73.17</v>
+        <v>78.05</v>
       </c>
       <c r="G4">
-        <v>26.83</v>
+        <v>21.95</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6861,7 +6864,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -6870,19 +6873,19 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>78.05</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="G5">
-        <v>21.95</v>
+        <v>17.07</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6893,10 +6896,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6">
         <v>41</v>
@@ -6914,7 +6917,7 @@
         <v>17.07</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6925,28 +6928,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7">
         <v>41</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>82.93000000000001</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="G7">
-        <v>17.07</v>
+        <v>7.32</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6962,7 +6965,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6987,826 +6990,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920124</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920343</v>
-      </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920342</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920125</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920126</v>
-      </c>
-      <c r="B6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920344</v>
-      </c>
-      <c r="B7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" t="s">
-        <v>141</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920127</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>142</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920424</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920345</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920128</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" t="s">
-        <v>145</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920130</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" t="s">
-        <v>146</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920131</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D13" t="s">
-        <v>147</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920132</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920133</v>
-      </c>
-      <c r="B15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" t="s">
-        <v>149</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920134</v>
-      </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" t="s">
-        <v>150</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920135</v>
-      </c>
-      <c r="B17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" t="s">
-        <v>112</v>
-      </c>
-      <c r="D17" t="s">
-        <v>151</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920244</v>
-      </c>
-      <c r="B18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D18" t="s">
-        <v>152</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920346</v>
-      </c>
-      <c r="B19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" t="s">
-        <v>153</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920129</v>
-      </c>
-      <c r="B20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" t="s">
-        <v>154</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920247</v>
-      </c>
-      <c r="B21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" t="s">
-        <v>120</v>
-      </c>
-      <c r="D21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920347</v>
-      </c>
-      <c r="B22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" t="s">
-        <v>156</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920136</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D23" t="s">
-        <v>157</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920349</v>
-      </c>
-      <c r="B24" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" t="s">
-        <v>123</v>
-      </c>
-      <c r="D24" t="s">
-        <v>158</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920137</v>
-      </c>
-      <c r="B25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" t="s">
-        <v>124</v>
-      </c>
-      <c r="D25" t="s">
-        <v>159</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920350</v>
-      </c>
-      <c r="B26" t="s">
-        <v>94</v>
-      </c>
-      <c r="C26" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" t="s">
-        <v>160</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920138</v>
-      </c>
-      <c r="B27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" t="s">
-        <v>161</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920110</v>
-      </c>
-      <c r="B28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C28" t="s">
-        <v>120</v>
-      </c>
-      <c r="D28" t="s">
-        <v>162</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920140</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" t="s">
-        <v>163</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920352</v>
-      </c>
-      <c r="B30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" t="s">
-        <v>164</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920252</v>
-      </c>
-      <c r="B31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" t="s">
-        <v>127</v>
-      </c>
-      <c r="D31" t="s">
-        <v>165</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920142</v>
-      </c>
-      <c r="B32" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" t="s">
-        <v>128</v>
-      </c>
-      <c r="D32" t="s">
-        <v>166</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920353</v>
-      </c>
-      <c r="B33" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" t="s">
-        <v>108</v>
-      </c>
-      <c r="D33" t="s">
-        <v>167</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920354</v>
-      </c>
-      <c r="B34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" t="s">
-        <v>129</v>
-      </c>
-      <c r="D34" t="s">
-        <v>168</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920143</v>
-      </c>
-      <c r="B35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" t="s">
-        <v>169</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920144</v>
-      </c>
-      <c r="B36" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36" t="s">
-        <v>170</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920145</v>
-      </c>
-      <c r="B37" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" t="s">
-        <v>131</v>
-      </c>
-      <c r="D37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>22330051920146</v>
-      </c>
-      <c r="B38" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" t="s">
-        <v>81</v>
-      </c>
-      <c r="D38" t="s">
-        <v>172</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>22330051920258</v>
-      </c>
-      <c r="B39" t="s">
-        <v>106</v>
-      </c>
-      <c r="C39" t="s">
-        <v>132</v>
-      </c>
-      <c r="D39" t="s">
-        <v>173</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>22330051920355</v>
-      </c>
-      <c r="B40" t="s">
-        <v>107</v>
-      </c>
-      <c r="C40" t="s">
-        <v>133</v>
-      </c>
-      <c r="D40" t="s">
-        <v>174</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>22330051920147</v>
-      </c>
-      <c r="B41" t="s">
-        <v>108</v>
-      </c>
-      <c r="C41" t="s">
-        <v>134</v>
-      </c>
-      <c r="D41" t="s">
-        <v>175</v>
-      </c>
-      <c r="E41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>22330051920148</v>
-      </c>
-      <c r="B42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C42" t="s">
-        <v>135</v>
-      </c>
-      <c r="D42" t="s">
-        <v>176</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -7854,7 +7037,7 @@
         <v>136</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -7871,7 +7054,7 @@
         <v>137</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7888,7 +7071,7 @@
         <v>138</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7905,7 +7088,7 @@
         <v>139</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7922,7 +7105,7 @@
         <v>140</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7939,7 +7122,7 @@
         <v>141</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7956,7 +7139,7 @@
         <v>142</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7973,7 +7156,7 @@
         <v>143</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7990,7 +7173,7 @@
         <v>144</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8007,7 +7190,7 @@
         <v>145</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -8024,7 +7207,7 @@
         <v>146</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8041,7 +7224,7 @@
         <v>147</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -8058,7 +7241,7 @@
         <v>148</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -8075,7 +7258,7 @@
         <v>149</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -8092,7 +7275,7 @@
         <v>150</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8109,7 +7292,7 @@
         <v>151</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8126,7 +7309,7 @@
         <v>152</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8143,7 +7326,7 @@
         <v>153</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8160,7 +7343,7 @@
         <v>154</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8177,7 +7360,7 @@
         <v>155</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8194,7 +7377,7 @@
         <v>156</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8211,7 +7394,7 @@
         <v>157</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8228,7 +7411,7 @@
         <v>158</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8245,7 +7428,7 @@
         <v>159</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8262,7 +7445,7 @@
         <v>160</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8279,7 +7462,7 @@
         <v>161</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8296,7 +7479,7 @@
         <v>162</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8313,7 +7496,7 @@
         <v>163</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8330,7 +7513,7 @@
         <v>164</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8347,7 +7530,7 @@
         <v>165</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -8364,7 +7547,7 @@
         <v>166</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8381,7 +7564,7 @@
         <v>167</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8398,7 +7581,7 @@
         <v>168</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8415,7 +7598,7 @@
         <v>169</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8432,7 +7615,7 @@
         <v>170</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -8449,7 +7632,7 @@
         <v>171</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -8466,7 +7649,7 @@
         <v>172</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -8483,7 +7666,7 @@
         <v>173</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -8500,7 +7683,7 @@
         <v>174</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -8517,7 +7700,7 @@
         <v>175</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -8534,7 +7717,7 @@
         <v>176</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8544,7 +7727,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8576,45 +7759,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920343</v>
+        <v>22330051920126</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>65</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920343</v>
+        <v>22330051920126</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -8622,42 +7805,42 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920344</v>
+        <v>22330051920132</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>65</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920344</v>
+        <v>22330051920132</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
@@ -8668,19 +7851,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920130</v>
+        <v>22330051920354</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>65</v>
@@ -8691,577 +7874,186 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920130</v>
+        <v>22330051920354</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>65</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920124</v>
+        <v>22330051920144</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920125</v>
+        <v>22330051920144</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>65</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920127</v>
+        <v>22330051920145</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>65</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920345</v>
+        <v>22330051920145</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>65</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920128</v>
+        <v>22330051920343</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920131</v>
+        <v>22330051920344</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>65</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920133</v>
+        <v>22330051920130</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>65</v>
       </c>
       <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920134</v>
-      </c>
-      <c r="B15" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" t="s">
-        <v>150</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920135</v>
-      </c>
-      <c r="B16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920129</v>
-      </c>
-      <c r="B17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D17" t="s">
-        <v>154</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920347</v>
-      </c>
-      <c r="B18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D18" t="s">
-        <v>156</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920349</v>
-      </c>
-      <c r="B19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" t="s">
-        <v>158</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920137</v>
-      </c>
-      <c r="B20" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" t="s">
-        <v>159</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920350</v>
-      </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" t="s">
-        <v>125</v>
-      </c>
-      <c r="D21" t="s">
-        <v>160</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920138</v>
-      </c>
-      <c r="B22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" t="s">
-        <v>117</v>
-      </c>
-      <c r="D22" t="s">
-        <v>161</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>65</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920110</v>
-      </c>
-      <c r="B23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" t="s">
-        <v>120</v>
-      </c>
-      <c r="D23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920140</v>
-      </c>
-      <c r="B24" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" t="s">
-        <v>126</v>
-      </c>
-      <c r="D24" t="s">
-        <v>163</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>65</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920252</v>
-      </c>
-      <c r="B25" t="s">
-        <v>99</v>
-      </c>
-      <c r="C25" t="s">
-        <v>127</v>
-      </c>
-      <c r="D25" t="s">
-        <v>165</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>65</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920142</v>
-      </c>
-      <c r="B26" t="s">
-        <v>100</v>
-      </c>
-      <c r="C26" t="s">
-        <v>128</v>
-      </c>
-      <c r="D26" t="s">
-        <v>166</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920143</v>
-      </c>
-      <c r="B27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" t="s">
-        <v>110</v>
-      </c>
-      <c r="D27" t="s">
-        <v>169</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920146</v>
-      </c>
-      <c r="B28" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" t="s">
-        <v>172</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>65</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920355</v>
-      </c>
-      <c r="B29" t="s">
-        <v>107</v>
-      </c>
-      <c r="C29" t="s">
-        <v>133</v>
-      </c>
-      <c r="D29" t="s">
-        <v>174</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>65</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920147</v>
-      </c>
-      <c r="B30" t="s">
-        <v>108</v>
-      </c>
-      <c r="C30" t="s">
-        <v>134</v>
-      </c>
-      <c r="D30" t="s">
-        <v>175</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>65</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920148</v>
-      </c>
-      <c r="B31" t="s">
-        <v>109</v>
-      </c>
-      <c r="C31" t="s">
-        <v>135</v>
-      </c>
-      <c r="D31" t="s">
-        <v>176</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>65</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2BLCM - Estadisticos 20222.xlsx
+++ b/grupos/2BLCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="181">
   <si>
     <t>Materia</t>
   </si>
@@ -216,10 +216,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>NC</t>
@@ -6803,7 +6815,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3">
         <v>41</v>
@@ -6835,7 +6847,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4">
         <v>41</v>
@@ -6867,7 +6879,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C5">
         <v>41</v>
@@ -6899,7 +6911,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C6">
         <v>41</v>
@@ -6931,7 +6943,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C7">
         <v>41</v>
@@ -6974,16 +6986,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -7008,16 +7020,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>63</v>
@@ -7028,13 +7040,13 @@
         <v>22330051920124</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -7045,13 +7057,13 @@
         <v>22330051920343</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -7062,13 +7074,13 @@
         <v>22330051920342</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -7079,13 +7091,13 @@
         <v>22330051920125</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -7096,13 +7108,13 @@
         <v>22330051920126</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -7113,13 +7125,13 @@
         <v>22330051920344</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7130,13 +7142,13 @@
         <v>22330051920127</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -7147,13 +7159,13 @@
         <v>22330051920424</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -7164,13 +7176,13 @@
         <v>22330051920345</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -7181,13 +7193,13 @@
         <v>22330051920128</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -7198,13 +7210,13 @@
         <v>22330051920130</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -7215,13 +7227,13 @@
         <v>22330051920131</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -7232,13 +7244,13 @@
         <v>22330051920132</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -7249,13 +7261,13 @@
         <v>22330051920133</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -7266,13 +7278,13 @@
         <v>22330051920134</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -7283,13 +7295,13 @@
         <v>22330051920135</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -7300,13 +7312,13 @@
         <v>22330051920244</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -7317,13 +7329,13 @@
         <v>22330051920346</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -7334,13 +7346,13 @@
         <v>22330051920129</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -7351,13 +7363,13 @@
         <v>22330051920247</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D21" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -7368,13 +7380,13 @@
         <v>22330051920347</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -7385,13 +7397,13 @@
         <v>22330051920136</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -7402,13 +7414,13 @@
         <v>22330051920349</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -7419,13 +7431,13 @@
         <v>22330051920137</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -7436,13 +7448,13 @@
         <v>22330051920350</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D26" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -7453,13 +7465,13 @@
         <v>22330051920138</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -7470,13 +7482,13 @@
         <v>22330051920110</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -7487,13 +7499,13 @@
         <v>22330051920140</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -7504,13 +7516,13 @@
         <v>22330051920352</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D30" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -7521,13 +7533,13 @@
         <v>22330051920252</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D31" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -7538,13 +7550,13 @@
         <v>22330051920142</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -7555,13 +7567,13 @@
         <v>22330051920353</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -7572,13 +7584,13 @@
         <v>22330051920354</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C34" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D34" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -7589,13 +7601,13 @@
         <v>22330051920143</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D35" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -7606,13 +7618,13 @@
         <v>22330051920144</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C36" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D36" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -7623,13 +7635,13 @@
         <v>22330051920145</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C37" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -7640,13 +7652,13 @@
         <v>22330051920146</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D38" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -7657,13 +7669,13 @@
         <v>22330051920258</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D39" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -7674,13 +7686,13 @@
         <v>22330051920355</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -7691,13 +7703,13 @@
         <v>22330051920147</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D41" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -7708,13 +7720,13 @@
         <v>22330051920148</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C42" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D42" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -7736,16 +7748,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -7762,13 +7774,13 @@
         <v>22330051920126</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -7785,19 +7797,19 @@
         <v>22330051920126</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7808,13 +7820,13 @@
         <v>22330051920132</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -7831,19 +7843,19 @@
         <v>22330051920132</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7854,13 +7866,13 @@
         <v>22330051920354</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -7877,19 +7889,19 @@
         <v>22330051920354</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7900,19 +7912,19 @@
         <v>22330051920144</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D8" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7923,19 +7935,19 @@
         <v>22330051920144</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D9" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7946,13 +7958,13 @@
         <v>22330051920145</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D10" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -7969,19 +7981,19 @@
         <v>22330051920145</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7992,19 +8004,19 @@
         <v>22330051920343</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -8015,13 +8027,13 @@
         <v>22330051920344</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -8038,19 +8050,19 @@
         <v>22330051920130</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>5</v>

--- a/grupos/2BLCM - Estadisticos 20222.xlsx
+++ b/grupos/2BLCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="184">
   <si>
     <t>Materia</t>
   </si>
@@ -117,6 +117,9 @@
     <t>LUNA VAZQUEZ KAREN</t>
   </si>
   <si>
+    <t>MALDONADO RAMON JOSE ALBIN</t>
+  </si>
+  <si>
     <t>MARCIAL ACAHUA ALANIS YUMEI</t>
   </si>
   <si>
@@ -306,6 +309,9 @@
     <t>MARCIAL</t>
   </si>
   <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
     <t>MAY</t>
   </si>
   <si>
@@ -399,6 +405,9 @@
     <t>ACAHUA</t>
   </si>
   <si>
+    <t>RAMON</t>
+  </si>
+  <si>
     <t>SERRANO</t>
   </si>
   <si>
@@ -420,9 +429,6 @@
     <t>REYES</t>
   </si>
   <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
     <t>MEZA</t>
   </si>
   <si>
@@ -502,6 +508,9 @@
   </si>
   <si>
     <t>ALANIS YUMEI</t>
+  </si>
+  <si>
+    <t>JOSE ALBIN</t>
   </si>
   <si>
     <t>GABRIELA AIMEE</t>
@@ -919,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -2587,22 +2596,22 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24">
         <v>10</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24">
         <v>10</v>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2641,22 +2650,22 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>10</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2664,22 +2673,22 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2718,22 +2727,22 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2741,22 +2750,22 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2795,22 +2804,22 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2818,22 +2827,22 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>10</v>
       </c>
       <c r="F27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2872,22 +2881,22 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2895,11 +2904,11 @@
         <v>36</v>
       </c>
       <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28">
         <v>9</v>
       </c>
-      <c r="C28">
-        <v>10</v>
-      </c>
       <c r="D28">
         <v>8</v>
       </c>
@@ -2907,10 +2916,10 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2949,11 +2958,11 @@
         <v>-1</v>
       </c>
       <c r="T28">
+        <v>8</v>
+      </c>
+      <c r="U28">
         <v>9</v>
       </c>
-      <c r="U28">
-        <v>10</v>
-      </c>
       <c r="V28">
         <v>8</v>
       </c>
@@ -2961,10 +2970,10 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2972,22 +2981,22 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -3026,22 +3035,22 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3049,22 +3058,22 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>6</v>
       </c>
       <c r="E30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H30">
         <v>-1</v>
@@ -3103,22 +3112,22 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>6</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3126,22 +3135,22 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31">
         <v>6</v>
       </c>
       <c r="F31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3180,22 +3189,22 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>6</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3203,22 +3212,22 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3257,22 +3266,22 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3280,22 +3289,22 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33">
         <v>10</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33">
         <v>9</v>
       </c>
       <c r="G33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3334,22 +3343,22 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>10</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3360,19 +3369,19 @@
         <v>7</v>
       </c>
       <c r="C34">
+        <v>10</v>
+      </c>
+      <c r="D34">
+        <v>10</v>
+      </c>
+      <c r="E34">
         <v>9</v>
       </c>
-      <c r="D34">
-        <v>6</v>
-      </c>
-      <c r="E34">
-        <v>6</v>
-      </c>
       <c r="F34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H34">
         <v>-1</v>
@@ -3414,19 +3423,19 @@
         <v>7</v>
       </c>
       <c r="U34">
+        <v>10</v>
+      </c>
+      <c r="V34">
+        <v>10</v>
+      </c>
+      <c r="W34">
         <v>9</v>
       </c>
-      <c r="V34">
-        <v>6</v>
-      </c>
-      <c r="W34">
-        <v>6</v>
-      </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3434,76 +3443,76 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35">
+        <v>6</v>
+      </c>
+      <c r="F35">
+        <v>8</v>
+      </c>
+      <c r="G35">
+        <v>8</v>
+      </c>
+      <c r="H35">
+        <v>-1</v>
+      </c>
+      <c r="I35">
+        <v>-1</v>
+      </c>
+      <c r="J35">
+        <v>-1</v>
+      </c>
+      <c r="K35">
+        <v>-1</v>
+      </c>
+      <c r="L35">
+        <v>-1</v>
+      </c>
+      <c r="M35">
+        <v>-1</v>
+      </c>
+      <c r="N35">
+        <v>-1</v>
+      </c>
+      <c r="O35">
+        <v>-1</v>
+      </c>
+      <c r="P35">
+        <v>-1</v>
+      </c>
+      <c r="Q35">
+        <v>-1</v>
+      </c>
+      <c r="R35">
+        <v>-1</v>
+      </c>
+      <c r="S35">
+        <v>-1</v>
+      </c>
+      <c r="T35">
+        <v>7</v>
+      </c>
+      <c r="U35">
         <v>9</v>
       </c>
-      <c r="F35">
-        <v>9</v>
-      </c>
-      <c r="G35">
-        <v>5</v>
-      </c>
-      <c r="H35">
-        <v>-1</v>
-      </c>
-      <c r="I35">
-        <v>-1</v>
-      </c>
-      <c r="J35">
-        <v>-1</v>
-      </c>
-      <c r="K35">
-        <v>-1</v>
-      </c>
-      <c r="L35">
-        <v>-1</v>
-      </c>
-      <c r="M35">
-        <v>-1</v>
-      </c>
-      <c r="N35">
-        <v>-1</v>
-      </c>
-      <c r="O35">
-        <v>-1</v>
-      </c>
-      <c r="P35">
-        <v>-1</v>
-      </c>
-      <c r="Q35">
-        <v>-1</v>
-      </c>
-      <c r="R35">
-        <v>-1</v>
-      </c>
-      <c r="S35">
-        <v>-1</v>
-      </c>
-      <c r="T35">
-        <v>5</v>
-      </c>
-      <c r="U35">
-        <v>8</v>
-      </c>
       <c r="V35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3511,7 +3520,7 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>8</v>
@@ -3520,10 +3529,10 @@
         <v>5</v>
       </c>
       <c r="E36">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -3565,7 +3574,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U36">
         <v>8</v>
@@ -3574,10 +3583,10 @@
         <v>5</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -3588,22 +3597,22 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G37">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H37">
         <v>-1</v>
@@ -3642,22 +3651,22 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3665,22 +3674,22 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F38">
         <v>8</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H38">
         <v>-1</v>
@@ -3719,22 +3728,22 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W38">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>8</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3742,22 +3751,22 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H39">
         <v>-1</v>
@@ -3796,19 +3805,19 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>5</v>
@@ -3819,7 +3828,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C40">
         <v>6</v>
@@ -3828,13 +3837,13 @@
         <v>5</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40">
         <v>-1</v>
@@ -3873,7 +3882,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U40">
         <v>6</v>
@@ -3882,10 +3891,10 @@
         <v>5</v>
       </c>
       <c r="W40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -3896,22 +3905,22 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C41">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E41">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G41">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H41">
         <v>-1</v>
@@ -3950,22 +3959,22 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U41">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y41">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3979,16 +3988,16 @@
         <v>9</v>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H42">
         <v>-1</v>
@@ -4033,16 +4042,16 @@
         <v>9</v>
       </c>
       <c r="V42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y42">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4050,20 +4059,20 @@
         <v>51</v>
       </c>
       <c r="B43">
+        <v>7</v>
+      </c>
+      <c r="C43">
         <v>9</v>
       </c>
-      <c r="C43">
-        <v>10</v>
-      </c>
       <c r="D43">
+        <v>8</v>
+      </c>
+      <c r="E43">
+        <v>7</v>
+      </c>
+      <c r="F43">
         <v>9</v>
       </c>
-      <c r="E43">
-        <v>10</v>
-      </c>
-      <c r="F43">
-        <v>10</v>
-      </c>
       <c r="G43">
         <v>8</v>
       </c>
@@ -4104,19 +4113,19 @@
         <v>-1</v>
       </c>
       <c r="T43">
+        <v>7</v>
+      </c>
+      <c r="U43">
         <v>9</v>
       </c>
-      <c r="U43">
-        <v>10</v>
-      </c>
       <c r="V43">
+        <v>8</v>
+      </c>
+      <c r="W43">
+        <v>7</v>
+      </c>
+      <c r="X43">
         <v>9</v>
-      </c>
-      <c r="W43">
-        <v>10</v>
-      </c>
-      <c r="X43">
-        <v>10</v>
       </c>
       <c r="Y43">
         <v>8</v>
@@ -4127,75 +4136,152 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C44">
+        <v>10</v>
+      </c>
+      <c r="D44">
         <v>9</v>
       </c>
-      <c r="D44">
-        <v>7</v>
-      </c>
       <c r="E44">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F44">
+        <v>10</v>
+      </c>
+      <c r="G44">
+        <v>8</v>
+      </c>
+      <c r="H44">
+        <v>-1</v>
+      </c>
+      <c r="I44">
+        <v>-1</v>
+      </c>
+      <c r="J44">
+        <v>-1</v>
+      </c>
+      <c r="K44">
+        <v>-1</v>
+      </c>
+      <c r="L44">
+        <v>-1</v>
+      </c>
+      <c r="M44">
+        <v>-1</v>
+      </c>
+      <c r="N44">
+        <v>-1</v>
+      </c>
+      <c r="O44">
+        <v>-1</v>
+      </c>
+      <c r="P44">
+        <v>-1</v>
+      </c>
+      <c r="Q44">
+        <v>-1</v>
+      </c>
+      <c r="R44">
+        <v>-1</v>
+      </c>
+      <c r="S44">
+        <v>-1</v>
+      </c>
+      <c r="T44">
         <v>9</v>
       </c>
-      <c r="G44">
-        <v>7</v>
-      </c>
-      <c r="H44">
-        <v>-1</v>
-      </c>
-      <c r="I44">
-        <v>-1</v>
-      </c>
-      <c r="J44">
-        <v>-1</v>
-      </c>
-      <c r="K44">
-        <v>-1</v>
-      </c>
-      <c r="L44">
-        <v>-1</v>
-      </c>
-      <c r="M44">
-        <v>-1</v>
-      </c>
-      <c r="N44">
-        <v>-1</v>
-      </c>
-      <c r="O44">
-        <v>-1</v>
-      </c>
-      <c r="P44">
-        <v>-1</v>
-      </c>
-      <c r="Q44">
-        <v>-1</v>
-      </c>
-      <c r="R44">
-        <v>-1</v>
-      </c>
-      <c r="S44">
-        <v>-1</v>
-      </c>
-      <c r="T44">
-        <v>6</v>
-      </c>
       <c r="U44">
+        <v>10</v>
+      </c>
+      <c r="V44">
         <v>9</v>
       </c>
-      <c r="V44">
-        <v>7</v>
-      </c>
       <c r="W44">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X44">
+        <v>10</v>
+      </c>
+      <c r="Y44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25">
+      <c r="A45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45">
+        <v>6</v>
+      </c>
+      <c r="C45">
         <v>9</v>
       </c>
-      <c r="Y44">
+      <c r="D45">
+        <v>7</v>
+      </c>
+      <c r="E45">
+        <v>8</v>
+      </c>
+      <c r="F45">
+        <v>9</v>
+      </c>
+      <c r="G45">
+        <v>7</v>
+      </c>
+      <c r="H45">
+        <v>-1</v>
+      </c>
+      <c r="I45">
+        <v>-1</v>
+      </c>
+      <c r="J45">
+        <v>-1</v>
+      </c>
+      <c r="K45">
+        <v>-1</v>
+      </c>
+      <c r="L45">
+        <v>-1</v>
+      </c>
+      <c r="M45">
+        <v>-1</v>
+      </c>
+      <c r="N45">
+        <v>-1</v>
+      </c>
+      <c r="O45">
+        <v>-1</v>
+      </c>
+      <c r="P45">
+        <v>-1</v>
+      </c>
+      <c r="Q45">
+        <v>-1</v>
+      </c>
+      <c r="R45">
+        <v>-1</v>
+      </c>
+      <c r="S45">
+        <v>-1</v>
+      </c>
+      <c r="T45">
+        <v>6</v>
+      </c>
+      <c r="U45">
+        <v>9</v>
+      </c>
+      <c r="V45">
+        <v>7</v>
+      </c>
+      <c r="W45">
+        <v>8</v>
+      </c>
+      <c r="X45">
+        <v>9</v>
+      </c>
+      <c r="Y45">
         <v>7</v>
       </c>
     </row>
@@ -4212,7 +4298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -4221,7 +4307,7 @@
     <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4229,7 +4315,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -4237,7 +4323,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -5494,16 +5580,16 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="C24">
         <v>100</v>
       </c>
       <c r="D24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E24">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -5553,22 +5639,22 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C25">
         <v>100</v>
       </c>
       <c r="D25">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="E25">
         <v>100</v>
       </c>
       <c r="F25">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G25">
-        <v>88.3</v>
+        <v>100</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -5612,22 +5698,22 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C26">
         <v>100</v>
       </c>
       <c r="D26">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="E26">
         <v>100</v>
       </c>
       <c r="F26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G26">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -5730,7 +5816,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -5801,10 +5887,10 @@
         <v>100</v>
       </c>
       <c r="F29">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G29">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -5848,7 +5934,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -5860,10 +5946,10 @@
         <v>100</v>
       </c>
       <c r="F30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -5907,22 +5993,22 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C31">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="D31">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E31">
         <v>100</v>
       </c>
       <c r="F31">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G31">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -5966,22 +6052,22 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C32">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="D32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>100</v>
       </c>
       <c r="F32">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G32">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -6084,7 +6170,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -6143,7 +6229,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -6273,7 +6359,7 @@
         <v>100</v>
       </c>
       <c r="F37">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>100</v>
@@ -6326,13 +6412,13 @@
         <v>100</v>
       </c>
       <c r="D38">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E38">
         <v>100</v>
       </c>
       <c r="F38">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G38">
         <v>100</v>
@@ -6379,19 +6465,19 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C39">
         <v>100</v>
       </c>
       <c r="D39">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E39">
         <v>100</v>
       </c>
       <c r="F39">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G39">
         <v>100</v>
@@ -6438,13 +6524,13 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C40">
         <v>100</v>
       </c>
       <c r="D40">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E40">
         <v>100</v>
@@ -6453,7 +6539,7 @@
         <v>95</v>
       </c>
       <c r="G40">
-        <v>88.3</v>
+        <v>100</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -6497,22 +6583,22 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C41">
         <v>100</v>
       </c>
       <c r="D41">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E41">
         <v>100</v>
       </c>
       <c r="F41">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G41">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -6674,7 +6760,7 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -6689,42 +6775,101 @@
         <v>100</v>
       </c>
       <c r="G44">
+        <v>100</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19">
+      <c r="A45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45">
+        <v>115</v>
+      </c>
+      <c r="C45">
+        <v>100</v>
+      </c>
+      <c r="D45">
+        <v>120</v>
+      </c>
+      <c r="E45">
+        <v>100</v>
+      </c>
+      <c r="F45">
+        <v>100</v>
+      </c>
+      <c r="G45">
         <v>85</v>
       </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
-      <c r="P44">
-        <v>0</v>
-      </c>
-      <c r="Q44">
-        <v>0</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
         <v>0</v>
       </c>
     </row>
@@ -6751,31 +6896,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -6783,22 +6928,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>65.84999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="G2">
-        <v>34.15</v>
+        <v>33.33</v>
       </c>
       <c r="H2">
         <v>6.6</v>
@@ -6815,22 +6960,22 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>73.17</v>
+        <v>73.81</v>
       </c>
       <c r="G3">
-        <v>26.83</v>
+        <v>26.19</v>
       </c>
       <c r="H3">
         <v>6.7</v>
@@ -6847,25 +6992,25 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
         <v>9</v>
       </c>
       <c r="F4">
-        <v>78.05</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="G4">
-        <v>21.95</v>
+        <v>21.43</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6879,25 +7024,25 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
         <v>7</v>
       </c>
       <c r="F5">
-        <v>82.93000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="G5">
-        <v>17.07</v>
+        <v>16.67</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6911,22 +7056,22 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6">
         <v>7</v>
       </c>
       <c r="F6">
-        <v>82.93000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="G6">
-        <v>17.07</v>
+        <v>16.67</v>
       </c>
       <c r="H6">
         <v>7.5</v>
@@ -6943,25 +7088,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>92.68000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="G7">
-        <v>7.32</v>
+        <v>7.14</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6986,16 +7131,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -7011,7 +7156,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7020,19 +7165,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7040,13 +7185,13 @@
         <v>22330051920124</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -7057,13 +7202,13 @@
         <v>22330051920343</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -7074,13 +7219,13 @@
         <v>22330051920342</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -7091,13 +7236,13 @@
         <v>22330051920125</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -7108,13 +7253,13 @@
         <v>22330051920126</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -7125,13 +7270,13 @@
         <v>22330051920344</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7142,13 +7287,13 @@
         <v>22330051920127</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -7159,13 +7304,13 @@
         <v>22330051920424</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -7176,13 +7321,13 @@
         <v>22330051920345</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -7193,13 +7338,13 @@
         <v>22330051920128</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -7210,13 +7355,13 @@
         <v>22330051920130</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -7227,13 +7372,13 @@
         <v>22330051920131</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -7244,13 +7389,13 @@
         <v>22330051920132</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -7261,13 +7406,13 @@
         <v>22330051920133</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -7278,13 +7423,13 @@
         <v>22330051920134</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D16" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -7295,13 +7440,13 @@
         <v>22330051920135</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -7312,13 +7457,13 @@
         <v>22330051920244</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -7329,13 +7474,13 @@
         <v>22330051920346</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -7346,13 +7491,13 @@
         <v>22330051920129</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -7363,13 +7508,13 @@
         <v>22330051920247</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -7380,13 +7525,13 @@
         <v>22330051920347</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -7394,16 +7539,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920136</v>
+        <v>22330051920248</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -7411,16 +7556,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920349</v>
+        <v>22330051920136</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -7428,16 +7573,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920137</v>
+        <v>22330051920349</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -7445,16 +7590,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920350</v>
+        <v>22330051920137</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -7462,16 +7607,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920138</v>
+        <v>22330051920350</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D27" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -7479,16 +7624,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920110</v>
+        <v>22330051920138</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -7496,16 +7641,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920140</v>
+        <v>22330051920110</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -7513,16 +7658,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920352</v>
+        <v>22330051920140</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D30" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -7530,16 +7675,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920252</v>
+        <v>22330051920352</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D31" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -7547,16 +7692,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920142</v>
+        <v>22330051920252</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D32" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -7564,16 +7709,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920353</v>
+        <v>22330051920142</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -7581,16 +7726,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920354</v>
+        <v>22330051920353</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -7598,16 +7743,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920143</v>
+        <v>22330051920354</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -7615,16 +7760,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920144</v>
+        <v>22330051920143</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="D36" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -7632,16 +7777,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22330051920145</v>
+        <v>22330051920144</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -7649,16 +7794,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>22330051920146</v>
+        <v>22330051920145</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -7666,16 +7811,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>22330051920258</v>
+        <v>22330051920146</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="D39" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -7683,16 +7828,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>22330051920355</v>
+        <v>22330051920258</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D40" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -7700,16 +7845,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>22330051920147</v>
+        <v>22330051920355</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D41" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -7717,18 +7862,35 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
+        <v>22330051920147</v>
+      </c>
+      <c r="B42" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" t="s">
+        <v>182</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
         <v>22330051920148</v>
       </c>
-      <c r="B42" t="s">
-        <v>113</v>
-      </c>
-      <c r="C42" t="s">
-        <v>139</v>
-      </c>
-      <c r="D42" t="s">
-        <v>180</v>
-      </c>
-      <c r="E42">
+      <c r="B43" t="s">
+        <v>115</v>
+      </c>
+      <c r="C43" t="s">
+        <v>141</v>
+      </c>
+      <c r="D43" t="s">
+        <v>183</v>
+      </c>
+      <c r="E43">
         <v>0</v>
       </c>
     </row>
@@ -7748,22 +7910,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -7774,19 +7936,19 @@
         <v>22330051920126</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7797,19 +7959,19 @@
         <v>22330051920126</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7820,19 +7982,19 @@
         <v>22330051920132</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7843,19 +8005,19 @@
         <v>22330051920132</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7866,19 +8028,19 @@
         <v>22330051920354</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7889,19 +8051,19 @@
         <v>22330051920354</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7912,19 +8074,19 @@
         <v>22330051920144</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7935,19 +8097,19 @@
         <v>22330051920144</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7958,19 +8120,19 @@
         <v>22330051920145</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7981,19 +8143,19 @@
         <v>22330051920145</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -8004,19 +8166,19 @@
         <v>22330051920343</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -8027,19 +8189,19 @@
         <v>22330051920344</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -8050,19 +8212,19 @@
         <v>22330051920130</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14">
         <v>5</v>

--- a/grupos/2BLCM - Estadisticos 20222.xlsx
+++ b/grupos/2BLCM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="101">
   <si>
     <t>Materia</t>
   </si>
@@ -249,334 +248,88 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>TORRES</t>
   </si>
   <si>
     <t>ARZATE</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>APONTE</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
     <t>CABRERA</t>
   </si>
   <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>COLMENARES</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>SALAS</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
   </si>
   <si>
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>MAY</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>TENORIO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VIÑAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ZEPACTLE</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ACAHUA</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>MEZA</t>
   </si>
   <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>TOBIAS</t>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>AZUL ARIADNA</t>
+  </si>
+  <si>
+    <t>MELISA VIANNEY</t>
   </si>
   <si>
     <t>LUCIANA</t>
   </si>
   <si>
-    <t>LEONOR</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
-  </si>
-  <si>
     <t>DARA NAOMI</t>
   </si>
   <si>
-    <t>MAYRA</t>
-  </si>
-  <si>
-    <t>JULIO EDUARDO</t>
-  </si>
-  <si>
-    <t>JULIANA</t>
-  </si>
-  <si>
     <t>KARENT LILIANA</t>
   </si>
   <si>
     <t>ABIGAIL ANTONIA</t>
   </si>
   <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>MARIA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>DANNA ANGELA</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
-    <t>ILSE MARIA</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>ALANIS YUMEI</t>
-  </si>
-  <si>
-    <t>JOSE ALBIN</t>
-  </si>
-  <si>
-    <t>GABRIELA AIMEE</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>FELIX RAFAEL</t>
-  </si>
-  <si>
-    <t>JOSELYN</t>
-  </si>
-  <si>
-    <t>ZURI GABRIELA</t>
-  </si>
-  <si>
-    <t>ODALIS SOFIA</t>
-  </si>
-  <si>
-    <t>JESUS ADRIAN</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>JOSE JAVIER</t>
-  </si>
-  <si>
-    <t>ESTEFANY VIANEY</t>
-  </si>
-  <si>
-    <t>AZUL ARIADNA</t>
-  </si>
-  <si>
     <t>KEVIN</t>
   </si>
   <si>
-    <t>ORESTES</t>
-  </si>
-  <si>
     <t>ACSA FERNANDA</t>
-  </si>
-  <si>
-    <t>MELISA VIANNEY</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>NERY JOSELYN</t>
-  </si>
-  <si>
-    <t>REYNA LINDA</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>ISABEL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -629,11 +382,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1089,7 +843,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1125,7 +879,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1166,7 +920,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1202,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1243,7 +997,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1320,7 +1074,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1397,7 +1151,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1433,7 +1187,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1474,7 +1228,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1510,7 +1264,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1551,7 +1305,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1628,7 +1382,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1664,7 +1418,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1705,7 +1459,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1782,7 +1536,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1818,7 +1572,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1859,7 +1613,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1936,7 +1690,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -2013,7 +1767,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2049,7 +1803,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2090,7 +1844,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2167,7 +1921,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2244,7 +1998,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2321,7 +2075,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2357,7 +2111,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2398,7 +2152,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2475,7 +2229,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2552,7 +2306,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2629,7 +2383,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2665,7 +2419,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2706,7 +2460,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2783,7 +2537,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2819,7 +2573,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2860,7 +2614,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2937,7 +2691,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2973,7 +2727,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -3014,7 +2768,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3050,7 +2804,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3091,7 +2845,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3127,7 +2881,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3168,7 +2922,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3204,7 +2958,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3245,7 +2999,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3281,7 +3035,7 @@
         <v>5</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3322,7 +3076,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3358,7 +3112,7 @@
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3399,7 +3153,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3435,7 +3189,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3476,7 +3230,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3512,7 +3266,7 @@
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3553,7 +3307,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3589,7 +3343,7 @@
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3630,7 +3384,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3666,7 +3420,7 @@
         <v>7</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3707,7 +3461,7 @@
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3784,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3820,7 +3574,7 @@
         <v>8</v>
       </c>
       <c r="Y39">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3861,7 +3615,7 @@
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3938,7 +3692,7 @@
         <v>-1</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -4015,7 +3769,7 @@
         <v>-1</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4051,7 +3805,7 @@
         <v>10</v>
       </c>
       <c r="Y42">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4092,7 +3846,7 @@
         <v>-1</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4128,7 +3882,7 @@
         <v>9</v>
       </c>
       <c r="Y43">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4169,7 +3923,7 @@
         <v>-1</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -4205,7 +3959,7 @@
         <v>10</v>
       </c>
       <c r="Y44">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4246,7 +4000,7 @@
         <v>-1</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -4433,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -4492,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>101.7</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -4551,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>88.3</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -4610,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -4669,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -4728,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>108.3</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -4787,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -4846,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -4905,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4964,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>101.7</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -5023,7 +4777,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -5082,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>101.7</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -5141,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>108.3</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5200,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5259,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -5318,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -5377,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -5436,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -5495,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -5554,7 +5308,7 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>101.7</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -5613,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -5672,7 +5426,7 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -5731,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -5790,7 +5544,7 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -5849,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -5908,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -5967,7 +5721,7 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -6026,7 +5780,7 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>108.3</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -6085,7 +5839,7 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -6144,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -6203,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>116.7</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -6262,7 +6016,7 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -6321,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -6380,7 +6134,7 @@
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -6439,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>101.7</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -6498,7 +6252,7 @@
         <v>0</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -6557,7 +6311,7 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -6616,7 +6370,7 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>116.7</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -6675,7 +6429,7 @@
         <v>0</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N42">
         <v>0</v>
@@ -6734,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>116.7</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -6793,7 +6547,7 @@
         <v>0</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>116.7</v>
       </c>
       <c r="N44">
         <v>0</v>
@@ -6852,7 +6606,7 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N45">
         <v>0</v>
@@ -6889,6 +6643,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -6939,11 +6695,11 @@
       <c r="E2">
         <v>14</v>
       </c>
-      <c r="F2">
-        <v>66.67</v>
-      </c>
-      <c r="G2">
-        <v>33.33</v>
+      <c r="F2" s="2">
+        <v>66.7</v>
+      </c>
+      <c r="G2" s="2">
+        <v>33.3</v>
       </c>
       <c r="H2">
         <v>6.6</v>
@@ -6951,7 +6707,7 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6966,24 +6722,24 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>73.81</v>
-      </c>
-      <c r="G3">
-        <v>26.19</v>
+        <v>12</v>
+      </c>
+      <c r="F3" s="2">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="G3" s="2">
+        <v>28.6</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7003,11 +6759,11 @@
       <c r="E4">
         <v>9</v>
       </c>
-      <c r="F4">
-        <v>78.56999999999999</v>
-      </c>
-      <c r="G4">
-        <v>21.43</v>
+      <c r="F4" s="2">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="G4" s="2">
+        <v>21.4</v>
       </c>
       <c r="H4">
         <v>6.9</v>
@@ -7015,7 +6771,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7035,11 +6791,11 @@
       <c r="E5">
         <v>7</v>
       </c>
-      <c r="F5">
-        <v>83.33</v>
-      </c>
-      <c r="G5">
-        <v>16.67</v>
+      <c r="F5" s="2">
+        <v>83.3</v>
+      </c>
+      <c r="G5" s="2">
+        <v>16.7</v>
       </c>
       <c r="H5">
         <v>7.9</v>
@@ -7047,7 +6803,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7067,11 +6823,11 @@
       <c r="E6">
         <v>7</v>
       </c>
-      <c r="F6">
-        <v>83.33</v>
-      </c>
-      <c r="G6">
-        <v>16.67</v>
+      <c r="F6" s="2">
+        <v>83.3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>16.7</v>
       </c>
       <c r="H6">
         <v>7.5</v>
@@ -7079,7 +6835,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7099,11 +6855,11 @@
       <c r="E7">
         <v>3</v>
       </c>
-      <c r="F7">
-        <v>92.86</v>
-      </c>
-      <c r="G7">
-        <v>7.14</v>
+      <c r="F7" s="2">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="G7" s="2">
+        <v>7.1</v>
       </c>
       <c r="H7">
         <v>8.1</v>
@@ -7111,7 +6867,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7156,752 +6912,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>22330051920124</v>
-      </c>
-      <c r="B2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>22330051920343</v>
-      </c>
-      <c r="B3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>22330051920342</v>
-      </c>
-      <c r="B4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>22330051920125</v>
-      </c>
-      <c r="B5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>22330051920126</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>22330051920344</v>
-      </c>
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>22330051920127</v>
-      </c>
-      <c r="B8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" t="s">
-        <v>148</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>22330051920424</v>
-      </c>
-      <c r="B9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>22330051920345</v>
-      </c>
-      <c r="B10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>22330051920128</v>
-      </c>
-      <c r="B11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" t="s">
-        <v>151</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>22330051920130</v>
-      </c>
-      <c r="B12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" t="s">
-        <v>152</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>22330051920131</v>
-      </c>
-      <c r="B13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>22330051920132</v>
-      </c>
-      <c r="B14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>154</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>22330051920133</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" t="s">
-        <v>155</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>22330051920134</v>
-      </c>
-      <c r="B16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" t="s">
-        <v>122</v>
-      </c>
-      <c r="D16" t="s">
-        <v>156</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>22330051920135</v>
-      </c>
-      <c r="B17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" t="s">
-        <v>157</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>22330051920244</v>
-      </c>
-      <c r="B18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" t="s">
-        <v>158</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>22330051920346</v>
-      </c>
-      <c r="B19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" t="s">
-        <v>159</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>22330051920129</v>
-      </c>
-      <c r="B20" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" t="s">
-        <v>125</v>
-      </c>
-      <c r="D20" t="s">
-        <v>160</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>22330051920247</v>
-      </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" t="s">
-        <v>161</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>22330051920347</v>
-      </c>
-      <c r="B22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" t="s">
-        <v>162</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>22330051920248</v>
-      </c>
-      <c r="B23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" t="s">
-        <v>128</v>
-      </c>
-      <c r="D23" t="s">
-        <v>163</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>22330051920136</v>
-      </c>
-      <c r="B24" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" t="s">
-        <v>164</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>22330051920349</v>
-      </c>
-      <c r="B25" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" t="s">
-        <v>130</v>
-      </c>
-      <c r="D25" t="s">
-        <v>165</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>22330051920137</v>
-      </c>
-      <c r="B26" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" t="s">
-        <v>131</v>
-      </c>
-      <c r="D26" t="s">
-        <v>166</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>22330051920350</v>
-      </c>
-      <c r="B27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C27" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" t="s">
-        <v>167</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>22330051920138</v>
-      </c>
-      <c r="B28" t="s">
-        <v>101</v>
-      </c>
-      <c r="C28" t="s">
-        <v>123</v>
-      </c>
-      <c r="D28" t="s">
-        <v>168</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>22330051920110</v>
-      </c>
-      <c r="B29" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" t="s">
-        <v>169</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>22330051920140</v>
-      </c>
-      <c r="B30" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" t="s">
-        <v>133</v>
-      </c>
-      <c r="D30" t="s">
-        <v>170</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>22330051920352</v>
-      </c>
-      <c r="B31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C31" t="s">
-        <v>116</v>
-      </c>
-      <c r="D31" t="s">
-        <v>171</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>22330051920252</v>
-      </c>
-      <c r="B32" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" t="s">
-        <v>134</v>
-      </c>
-      <c r="D32" t="s">
-        <v>172</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>22330051920142</v>
-      </c>
-      <c r="B33" t="s">
-        <v>106</v>
-      </c>
-      <c r="C33" t="s">
-        <v>135</v>
-      </c>
-      <c r="D33" t="s">
-        <v>173</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>22330051920353</v>
-      </c>
-      <c r="B34" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" t="s">
-        <v>174</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>22330051920354</v>
-      </c>
-      <c r="B35" t="s">
-        <v>108</v>
-      </c>
-      <c r="C35" t="s">
-        <v>96</v>
-      </c>
-      <c r="D35" t="s">
-        <v>175</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>22330051920143</v>
-      </c>
-      <c r="B36" t="s">
-        <v>109</v>
-      </c>
-      <c r="C36" t="s">
-        <v>116</v>
-      </c>
-      <c r="D36" t="s">
-        <v>176</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
-        <v>22330051920144</v>
-      </c>
-      <c r="B37" t="s">
-        <v>110</v>
-      </c>
-      <c r="C37" t="s">
-        <v>136</v>
-      </c>
-      <c r="D37" t="s">
-        <v>177</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>22330051920145</v>
-      </c>
-      <c r="B38" t="s">
-        <v>110</v>
-      </c>
-      <c r="C38" t="s">
-        <v>137</v>
-      </c>
-      <c r="D38" t="s">
-        <v>178</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39">
-        <v>22330051920146</v>
-      </c>
-      <c r="B39" t="s">
-        <v>111</v>
-      </c>
-      <c r="C39" t="s">
-        <v>86</v>
-      </c>
-      <c r="D39" t="s">
-        <v>179</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40">
-        <v>22330051920258</v>
-      </c>
-      <c r="B40" t="s">
-        <v>112</v>
-      </c>
-      <c r="C40" t="s">
-        <v>138</v>
-      </c>
-      <c r="D40" t="s">
-        <v>180</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41">
-        <v>22330051920355</v>
-      </c>
-      <c r="B41" t="s">
-        <v>113</v>
-      </c>
-      <c r="C41" t="s">
-        <v>139</v>
-      </c>
-      <c r="D41" t="s">
-        <v>181</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42">
-        <v>22330051920147</v>
-      </c>
-      <c r="B42" t="s">
-        <v>114</v>
-      </c>
-      <c r="C42" t="s">
-        <v>140</v>
-      </c>
-      <c r="D42" t="s">
-        <v>182</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43">
-        <v>22330051920148</v>
-      </c>
-      <c r="B43" t="s">
-        <v>115</v>
-      </c>
-      <c r="C43" t="s">
-        <v>141</v>
-      </c>
-      <c r="D43" t="s">
-        <v>183</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7933,16 +6944,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920126</v>
+        <v>22330051920132</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -7956,22 +6967,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920126</v>
+        <v>22330051920132</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7979,22 +6990,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920132</v>
+        <v>22330051920353</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>154</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -8002,22 +7013,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920132</v>
+        <v>22330051920353</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -8025,16 +7036,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920354</v>
+        <v>22330051920145</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -8048,16 +7059,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920354</v>
+        <v>22330051920145</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>175</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -8071,16 +7082,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920144</v>
+        <v>22330051920343</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>177</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -8094,22 +7105,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920144</v>
+        <v>22330051920344</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -8117,22 +7128,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920145</v>
+        <v>22330051920128</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -8140,22 +7151,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920145</v>
+        <v>22330051920130</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>178</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -8163,22 +7174,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920343</v>
+        <v>22330051920354</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -8186,47 +7197,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920344</v>
+        <v>22330051920144</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920130</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D14" t="s">
-        <v>152</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2BLCM - Estadisticos 20222.xlsx
+++ b/grupos/2BLCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -224,12 +224,12 @@
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -248,79 +248,49 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>ROSETE</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ARZATE</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>SOLANO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
+    <t>DARA NAOMI</t>
+  </si>
+  <si>
+    <t>KARENT LILIANA</t>
+  </si>
+  <si>
+    <t>ABIGAIL ANTONIA</t>
   </si>
   <si>
     <t>AZUL ARIADNA</t>
   </si>
   <si>
-    <t>MELISA VIANNEY</t>
-  </si>
-  <si>
-    <t>LUCIANA</t>
-  </si>
-  <si>
-    <t>DARA NAOMI</t>
-  </si>
-  <si>
-    <t>KARENT LILIANA</t>
-  </si>
-  <si>
-    <t>ABIGAIL ANTONIA</t>
-  </si>
-  <si>
     <t>KEVIN</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -831,16 +801,16 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>9</v>
@@ -876,7 +846,7 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -908,16 +878,16 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -985,16 +955,16 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -1021,7 +991,7 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1062,16 +1032,16 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
         <v>7</v>
@@ -1098,16 +1068,16 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1139,16 +1109,16 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>5</v>
@@ -1175,16 +1145,16 @@
         <v>6</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>5</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1216,16 +1186,16 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>5</v>
@@ -1258,7 +1228,7 @@
         <v>5</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1293,16 +1263,16 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -1329,13 +1299,13 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>5</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -1370,16 +1340,16 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1409,10 +1379,10 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1447,16 +1417,16 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -1524,16 +1494,16 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -1560,16 +1530,16 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>8</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1601,16 +1571,16 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>6</v>
@@ -1637,16 +1607,16 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1678,16 +1648,16 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>6</v>
@@ -1714,13 +1684,13 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>6</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1755,16 +1725,16 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>8</v>
@@ -1794,7 +1764,7 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1832,16 +1802,16 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>7</v>
@@ -1868,7 +1838,7 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -1877,7 +1847,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -1909,16 +1879,16 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -1954,7 +1924,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -1986,16 +1956,16 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -2063,16 +2033,16 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2102,10 +2072,10 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2140,16 +2110,16 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>3</v>
@@ -2217,16 +2187,16 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>3</v>
@@ -2262,7 +2232,7 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2294,16 +2264,16 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -2336,10 +2306,10 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2371,16 +2341,16 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>4</v>
@@ -2407,16 +2377,16 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>6</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2448,16 +2418,16 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
         <v>10</v>
@@ -2490,7 +2460,7 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2525,16 +2495,16 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>3</v>
@@ -2570,7 +2540,7 @@
         <v>5</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2602,16 +2572,16 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>8</v>
@@ -2638,16 +2608,16 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2679,16 +2649,16 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>10</v>
@@ -2715,10 +2685,10 @@
         <v>8</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -2756,16 +2726,16 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -2795,7 +2765,7 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -2833,16 +2803,16 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
         <v>7</v>
@@ -2910,16 +2880,16 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>8</v>
@@ -2949,10 +2919,10 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -2987,16 +2957,16 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>3</v>
@@ -3064,16 +3034,16 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -3103,7 +3073,7 @@
         <v>9</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -3141,16 +3111,16 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>10</v>
@@ -3186,7 +3156,7 @@
         <v>9</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>9</v>
@@ -3218,16 +3188,16 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -3254,10 +3224,10 @@
         <v>7</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W35">
         <v>6</v>
@@ -3295,16 +3265,16 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
         <v>10</v>
@@ -3331,10 +3301,10 @@
         <v>5</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>9</v>
@@ -3372,16 +3342,16 @@
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>7</v>
@@ -3408,16 +3378,16 @@
         <v>6</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>5</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -3449,16 +3419,16 @@
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M38">
         <v>7</v>
@@ -3491,10 +3461,10 @@
         <v>6</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y38">
         <v>7</v>
@@ -3526,16 +3496,16 @@
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>9</v>
@@ -3565,10 +3535,10 @@
         <v>10</v>
       </c>
       <c r="V39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X39">
         <v>8</v>
@@ -3603,16 +3573,16 @@
         <v>-1</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M40">
         <v>8</v>
@@ -3648,7 +3618,7 @@
         <v>7</v>
       </c>
       <c r="X40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -3680,16 +3650,16 @@
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>3</v>
@@ -3757,16 +3727,16 @@
         <v>-1</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M42">
         <v>8</v>
@@ -3796,13 +3766,13 @@
         <v>9</v>
       </c>
       <c r="V42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y42">
         <v>8</v>
@@ -3834,16 +3804,16 @@
         <v>-1</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M43">
         <v>9</v>
@@ -3873,13 +3843,13 @@
         <v>9</v>
       </c>
       <c r="V43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W43">
         <v>7</v>
       </c>
       <c r="X43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y43">
         <v>9</v>
@@ -3911,16 +3881,16 @@
         <v>-1</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M44">
         <v>10</v>
@@ -3950,7 +3920,7 @@
         <v>10</v>
       </c>
       <c r="V44">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W44">
         <v>10</v>
@@ -3988,16 +3958,16 @@
         <v>-1</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M45">
         <v>7</v>
@@ -4030,7 +4000,7 @@
         <v>7</v>
       </c>
       <c r="W45">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X45">
         <v>9</v>
@@ -4175,16 +4145,16 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
         <v>115</v>
@@ -4234,16 +4204,16 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M5">
         <v>101.7</v>
@@ -4293,16 +4263,16 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M6">
         <v>88.3</v>
@@ -4352,16 +4322,16 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
         <v>110</v>
@@ -4411,16 +4381,16 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M8">
         <v>105</v>
@@ -4470,16 +4440,16 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M9">
         <v>108.3</v>
@@ -4529,16 +4499,16 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M10">
         <v>6.7</v>
@@ -4588,16 +4558,16 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>120</v>
@@ -4647,16 +4617,16 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
         <v>120</v>
@@ -4706,16 +4676,16 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
         <v>101.7</v>
@@ -4765,16 +4735,16 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M14">
         <v>110</v>
@@ -4824,16 +4794,16 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15">
         <v>101.7</v>
@@ -4883,16 +4853,16 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16">
         <v>108.3</v>
@@ -4942,16 +4912,16 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M17">
         <v>115</v>
@@ -5001,16 +4971,16 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
         <v>120</v>
@@ -5060,16 +5030,16 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
         <v>120</v>
@@ -5119,16 +5089,16 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20">
         <v>120</v>
@@ -5178,16 +5148,16 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -5237,16 +5207,16 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M22">
         <v>83.3</v>
@@ -5296,16 +5266,16 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M23">
         <v>101.7</v>
@@ -5355,16 +5325,16 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
         <v>105</v>
@@ -5414,16 +5384,16 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
         <v>120</v>
@@ -5473,16 +5443,16 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M26">
         <v>86.7</v>
@@ -5532,16 +5502,16 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
         <v>120</v>
@@ -5591,16 +5561,16 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
         <v>120</v>
@@ -5650,16 +5620,16 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29">
         <v>120</v>
@@ -5709,16 +5679,16 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -5768,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M31">
         <v>108.3</v>
@@ -5827,16 +5797,16 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M32">
         <v>83.3</v>
@@ -5886,16 +5856,16 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M33">
         <v>120</v>
@@ -5945,16 +5915,16 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M34">
         <v>116.7</v>
@@ -6004,16 +5974,16 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35">
         <v>120</v>
@@ -6063,16 +6033,16 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M36">
         <v>120</v>
@@ -6122,16 +6092,16 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M37">
         <v>120</v>
@@ -6181,16 +6151,16 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M38">
         <v>101.7</v>
@@ -6240,16 +6210,16 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39">
         <v>120</v>
@@ -6299,16 +6269,16 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M40">
         <v>113.3</v>
@@ -6358,16 +6328,16 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M41">
         <v>116.7</v>
@@ -6417,16 +6387,16 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M42">
         <v>120</v>
@@ -6476,16 +6446,16 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M43">
         <v>116.7</v>
@@ -6535,16 +6505,16 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M44">
         <v>116.7</v>
@@ -6594,16 +6564,16 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M45">
         <v>110</v>
@@ -6690,19 +6660,19 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2">
-        <v>66.7</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2">
-        <v>33.3</v>
+        <v>31</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6745,7 +6715,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -6766,7 +6736,7 @@
         <v>21.4</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6777,7 +6747,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
@@ -6786,19 +6756,19 @@
         <v>42</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2">
-        <v>83.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>16.7</v>
+        <v>21.4</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6830,7 +6800,7 @@
         <v>16.7</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6850,16 +6820,16 @@
         <v>42</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
-        <v>92.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="G7" s="2">
-        <v>7.1</v>
+        <v>14.3</v>
       </c>
       <c r="H7">
         <v>8.1</v>
@@ -6912,7 +6882,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6944,16 +6914,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920132</v>
+        <v>22330051920344</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -6967,16 +6937,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920132</v>
+        <v>22330051920128</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6990,22 +6960,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920353</v>
+        <v>22330051920130</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7016,19 +6986,19 @@
         <v>22330051920353</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7036,16 +7006,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920145</v>
+        <v>22330051920354</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -7054,167 +7024,6 @@
         <v>66</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920145</v>
-      </c>
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920343</v>
-      </c>
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920344</v>
-      </c>
-      <c r="B9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920128</v>
-      </c>
-      <c r="B10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920130</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920354</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920144</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2BLCM - Estadisticos 20222.xlsx
+++ b/grupos/2BLCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -221,15 +221,15 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -248,6 +248,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
     <t>CABRERA</t>
   </si>
   <si>
@@ -260,7 +263,7 @@
     <t>ROSETE</t>
   </si>
   <si>
-    <t>SOLANO</t>
+    <t>MALDONADO</t>
   </si>
   <si>
     <t>GARCIA</t>
@@ -275,7 +278,7 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>MALDONADO</t>
+    <t>KEVIN</t>
   </si>
   <si>
     <t>DARA NAOMI</t>
@@ -288,9 +291,6 @@
   </si>
   <si>
     <t>AZUL ARIADNA</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
   </si>
 </sst>
 </file>
@@ -798,7 +798,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>10</v>
@@ -834,7 +834,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -875,7 +875,7 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>8</v>
@@ -952,7 +952,7 @@
         <v>3</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -1029,7 +1029,7 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -1106,7 +1106,7 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>8</v>
@@ -1183,7 +1183,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -1260,7 +1260,7 @@
         <v>3</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>5</v>
@@ -1337,7 +1337,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>10</v>
@@ -1414,7 +1414,7 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>10</v>
@@ -1491,7 +1491,7 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>7</v>
@@ -1527,7 +1527,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -1568,7 +1568,7 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>9</v>
@@ -1645,7 +1645,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>5</v>
@@ -1722,7 +1722,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>8</v>
@@ -1758,7 +1758,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -1799,7 +1799,7 @@
         <v>3</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>5</v>
@@ -1835,7 +1835,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -1876,7 +1876,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>8</v>
@@ -1912,7 +1912,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -1953,7 +1953,7 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
         <v>10</v>
@@ -2030,7 +2030,7 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>10</v>
@@ -2107,7 +2107,7 @@
         <v>3</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -2184,7 +2184,7 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>6</v>
@@ -2220,7 +2220,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2261,7 +2261,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>6</v>
@@ -2338,7 +2338,7 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>8</v>
@@ -2374,7 +2374,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2415,7 +2415,7 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>10</v>
@@ -2569,7 +2569,7 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>9</v>
@@ -2646,7 +2646,7 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>10</v>
@@ -2682,7 +2682,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2723,7 +2723,7 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>10</v>
@@ -2759,7 +2759,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>10</v>
@@ -2800,7 +2800,7 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>7</v>
@@ -2836,7 +2836,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>7</v>
@@ -2877,7 +2877,7 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>8</v>
@@ -2913,7 +2913,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>8</v>
@@ -2954,7 +2954,7 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>6</v>
@@ -3031,7 +3031,7 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -3108,7 +3108,7 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>9</v>
@@ -3144,7 +3144,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>10</v>
@@ -3185,7 +3185,7 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>10</v>
@@ -3262,7 +3262,7 @@
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>6</v>
@@ -3339,7 +3339,7 @@
         <v>5</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>10</v>
@@ -3375,7 +3375,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U37">
         <v>9</v>
@@ -3416,7 +3416,7 @@
         <v>7</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I38">
         <v>6</v>
@@ -3452,7 +3452,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U38">
         <v>6</v>
@@ -3493,7 +3493,7 @@
         <v>5</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I39">
         <v>9</v>
@@ -3529,7 +3529,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U39">
         <v>10</v>
@@ -3570,7 +3570,7 @@
         <v>3</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>6</v>
@@ -3606,7 +3606,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U40">
         <v>6</v>
@@ -3647,7 +3647,7 @@
         <v>2</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I41">
         <v>6</v>
@@ -3724,7 +3724,7 @@
         <v>7</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I42">
         <v>9</v>
@@ -3801,7 +3801,7 @@
         <v>8</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I43">
         <v>8</v>
@@ -3878,7 +3878,7 @@
         <v>8</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I44">
         <v>10</v>
@@ -3914,7 +3914,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U44">
         <v>10</v>
@@ -3955,7 +3955,7 @@
         <v>7</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I45">
         <v>9</v>
@@ -4142,7 +4142,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -4201,7 +4201,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -4260,7 +4260,7 @@
         <v>75</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I6">
         <v>66.7</v>
@@ -4319,7 +4319,7 @@
         <v>91.7</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I7">
         <v>100</v>
@@ -4378,7 +4378,7 @@
         <v>95</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I8">
         <v>80</v>
@@ -4437,7 +4437,7 @@
         <v>88.3</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -4496,7 +4496,7 @@
         <v>66.7</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I10">
         <v>66.7</v>
@@ -4555,7 +4555,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -4614,7 +4614,7 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -4673,7 +4673,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I13">
         <v>80</v>
@@ -4732,7 +4732,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -4791,7 +4791,7 @@
         <v>81.7</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15">
         <v>86.7</v>
@@ -4850,7 +4850,7 @@
         <v>98.3</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -4909,7 +4909,7 @@
         <v>85</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I17">
         <v>80</v>
@@ -4968,7 +4968,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I18">
         <v>86.7</v>
@@ -5027,7 +5027,7 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -5086,7 +5086,7 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -5145,7 +5145,7 @@
         <v>88.3</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I21">
         <v>73.3</v>
@@ -5204,7 +5204,7 @@
         <v>83.3</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I22">
         <v>100</v>
@@ -5263,7 +5263,7 @@
         <v>88.3</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I23">
         <v>100</v>
@@ -5322,7 +5322,7 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I24">
         <v>100</v>
@@ -5381,7 +5381,7 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>100</v>
@@ -5440,7 +5440,7 @@
         <v>88.3</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I26">
         <v>66.7</v>
@@ -5499,7 +5499,7 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>100</v>
@@ -5558,7 +5558,7 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>100</v>
@@ -5617,7 +5617,7 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>100</v>
@@ -5676,7 +5676,7 @@
         <v>95</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30">
         <v>100</v>
@@ -5735,7 +5735,7 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31">
         <v>100</v>
@@ -5794,7 +5794,7 @@
         <v>83.3</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I32">
         <v>100</v>
@@ -5853,7 +5853,7 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I33">
         <v>100</v>
@@ -5912,7 +5912,7 @@
         <v>100</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I34">
         <v>86.7</v>
@@ -5971,7 +5971,7 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I35">
         <v>100</v>
@@ -6030,7 +6030,7 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I36">
         <v>100</v>
@@ -6089,7 +6089,7 @@
         <v>100</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I37">
         <v>100</v>
@@ -6148,7 +6148,7 @@
         <v>100</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I38">
         <v>100</v>
@@ -6207,7 +6207,7 @@
         <v>100</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I39">
         <v>100</v>
@@ -6266,7 +6266,7 @@
         <v>100</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I40">
         <v>100</v>
@@ -6325,7 +6325,7 @@
         <v>88.3</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I41">
         <v>93.3</v>
@@ -6384,7 +6384,7 @@
         <v>100</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I42">
         <v>100</v>
@@ -6443,7 +6443,7 @@
         <v>100</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I43">
         <v>100</v>
@@ -6502,7 +6502,7 @@
         <v>100</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I44">
         <v>100</v>
@@ -6561,7 +6561,7 @@
         <v>85</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I45">
         <v>100</v>
@@ -6683,7 +6683,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -6704,7 +6704,7 @@
         <v>28.6</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6715,7 +6715,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -6724,19 +6724,19 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2">
-        <v>78.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>21.4</v>
+        <v>28.6</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
@@ -6768,7 +6768,7 @@
         <v>21.4</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6882,7 +6882,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6914,7 +6914,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920344</v>
+        <v>22330051920354</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
@@ -6926,10 +6926,10 @@
         <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6937,22 +6937,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920128</v>
+        <v>22330051920354</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6960,22 +6960,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920130</v>
+        <v>22330051920344</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6983,22 +6983,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920353</v>
+        <v>22330051920128</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7006,24 +7006,47 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920354</v>
+        <v>22330051920130</v>
       </c>
       <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920353</v>
+      </c>
+      <c r="B7" t="s">
         <v>80</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>85</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>90</v>
       </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6">
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2BLCM - Estadisticos 20222.xlsx
+++ b/grupos/2BLCM - Estadisticos 20222.xlsx
@@ -2492,7 +2492,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>5</v>

--- a/grupos/2BLCM - Estadisticos 20222.xlsx
+++ b/grupos/2BLCM - Estadisticos 20222.xlsx
@@ -4124,16 +4124,16 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -4142,40 +4142,40 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="I4">
         <v>100</v>
       </c>
       <c r="J4">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4183,16 +4183,16 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C5">
         <v>100</v>
       </c>
       <c r="D5">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -4201,40 +4201,40 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>75</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I5">
         <v>100</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M5">
-        <v>101.7</v>
+        <v>91.7</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -4242,16 +4242,16 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
       <c r="D6">
-        <v>70</v>
+        <v>58.3</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F6">
         <v>65</v>
@@ -4260,40 +4260,40 @@
         <v>75</v>
       </c>
       <c r="H6">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I6">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="J6">
-        <v>30</v>
+        <v>45.5</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L6">
-        <v>80</v>
+        <v>72.5</v>
       </c>
       <c r="M6">
-        <v>88.3</v>
+        <v>74.2</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4301,16 +4301,16 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>100</v>
       </c>
       <c r="D7">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -4319,40 +4319,40 @@
         <v>91.7</v>
       </c>
       <c r="H7">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="I7">
         <v>100</v>
       </c>
       <c r="J7">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4360,16 +4360,16 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>100</v>
       </c>
       <c r="D8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -4378,40 +4378,40 @@
         <v>95</v>
       </c>
       <c r="H8">
+        <v>95.5</v>
+      </c>
+      <c r="I8">
         <v>90</v>
       </c>
-      <c r="I8">
-        <v>80</v>
-      </c>
       <c r="J8">
+        <v>95.5</v>
+      </c>
+      <c r="K8">
+        <v>98</v>
+      </c>
+      <c r="L8">
+        <v>97.5</v>
+      </c>
+      <c r="M8">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="N8">
+        <v>95.5</v>
+      </c>
+      <c r="O8">
         <v>90</v>
       </c>
-      <c r="K8">
-        <v>100</v>
-      </c>
-      <c r="L8">
-        <v>95</v>
-      </c>
-      <c r="M8">
-        <v>105</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
       <c r="P8">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4419,16 +4419,16 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
       <c r="D9">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -4437,40 +4437,40 @@
         <v>88.3</v>
       </c>
       <c r="H9">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I9">
         <v>100</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L9">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M9">
-        <v>108.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4478,16 +4478,16 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
       <c r="D10">
-        <v>70</v>
+        <v>58.3</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F10">
         <v>70</v>
@@ -4496,40 +4496,40 @@
         <v>66.7</v>
       </c>
       <c r="H10">
-        <v>25</v>
+        <v>56.8</v>
       </c>
       <c r="I10">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L10">
-        <v>25</v>
+        <v>47.5</v>
       </c>
       <c r="M10">
-        <v>6.7</v>
+        <v>33.3</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>56.8</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4537,16 +4537,16 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
       <c r="D11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -4555,7 +4555,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>85</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -4564,31 +4564,31 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4596,16 +4596,16 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>100</v>
       </c>
       <c r="D12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -4623,31 +4623,31 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4655,16 +4655,16 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
       </c>
       <c r="D13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -4673,40 +4673,40 @@
         <v>100</v>
       </c>
       <c r="H13">
+        <v>95.5</v>
+      </c>
+      <c r="I13">
         <v>90</v>
       </c>
-      <c r="I13">
-        <v>80</v>
-      </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
-        <v>101.7</v>
+        <v>91.7</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4714,16 +4714,16 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>100</v>
       </c>
       <c r="D14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -4741,31 +4741,31 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M14">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4773,16 +4773,16 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="C15">
         <v>100</v>
       </c>
       <c r="D15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F15">
         <v>90</v>
@@ -4791,40 +4791,40 @@
         <v>81.7</v>
       </c>
       <c r="H15">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="I15">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="J15">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M15">
-        <v>101.7</v>
+        <v>83.3</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4832,16 +4832,16 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C16">
         <v>100</v>
       </c>
       <c r="D16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E16">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -4850,7 +4850,7 @@
         <v>98.3</v>
       </c>
       <c r="H16">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -4859,31 +4859,31 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L16">
         <v>100</v>
       </c>
       <c r="M16">
-        <v>108.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4891,16 +4891,16 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="C17">
         <v>100</v>
       </c>
       <c r="D17">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F17">
         <v>95</v>
@@ -4909,40 +4909,40 @@
         <v>85</v>
       </c>
       <c r="H17">
-        <v>60</v>
+        <v>72.7</v>
       </c>
       <c r="I17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J17">
+        <v>81.8</v>
+      </c>
+      <c r="K17">
+        <v>98</v>
+      </c>
+      <c r="L17">
         <v>90</v>
       </c>
-      <c r="K17">
-        <v>100</v>
-      </c>
-      <c r="L17">
-        <v>85</v>
-      </c>
       <c r="M17">
-        <v>115</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4950,16 +4950,16 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C18">
         <v>100</v>
       </c>
       <c r="D18">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="E18">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -4968,40 +4968,40 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="I18">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -5009,16 +5009,16 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>100</v>
       </c>
       <c r="D19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F19">
         <v>100</v>
@@ -5036,31 +5036,31 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -5068,16 +5068,16 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <v>100</v>
       </c>
       <c r="D20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E20">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -5086,7 +5086,7 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -5095,31 +5095,31 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L20">
         <v>100</v>
       </c>
       <c r="M20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -5127,16 +5127,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>85</v>
+        <v>70.8</v>
       </c>
       <c r="C21">
         <v>86.7</v>
       </c>
       <c r="D21">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="E21">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F21">
         <v>70</v>
@@ -5145,40 +5145,40 @@
         <v>88.3</v>
       </c>
       <c r="H21">
-        <v>60</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I21">
-        <v>73.3</v>
+        <v>80</v>
       </c>
       <c r="J21">
-        <v>40</v>
+        <v>68.2</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L21">
-        <v>45</v>
+        <v>57.5</v>
       </c>
       <c r="M21">
-        <v>100</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>68.2</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -5186,16 +5186,16 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
       </c>
       <c r="D22">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F22">
         <v>100</v>
@@ -5204,40 +5204,40 @@
         <v>83.3</v>
       </c>
       <c r="H22">
-        <v>30</v>
+        <v>68.2</v>
       </c>
       <c r="I22">
         <v>100</v>
       </c>
       <c r="J22">
-        <v>10</v>
+        <v>31.8</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L22">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="M22">
-        <v>83.3</v>
+        <v>75.8</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>68.2</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -5245,16 +5245,16 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="C23">
         <v>100</v>
       </c>
       <c r="D23">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F23">
         <v>85</v>
@@ -5263,40 +5263,40 @@
         <v>88.3</v>
       </c>
       <c r="H23">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I23">
         <v>100</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L23">
         <v>85</v>
       </c>
       <c r="M23">
-        <v>101.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5304,16 +5304,16 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>95</v>
+        <v>79.2</v>
       </c>
       <c r="C24">
         <v>100</v>
       </c>
       <c r="D24">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="E24">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -5322,13 +5322,13 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>80</v>
+        <v>79.5</v>
       </c>
       <c r="I24">
         <v>100</v>
       </c>
       <c r="J24">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -5337,25 +5337,25 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>105</v>
+        <v>93.2</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>79.5</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5363,16 +5363,16 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
       </c>
       <c r="D25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E25">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -5390,31 +5390,31 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5422,16 +5422,16 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="C26">
         <v>100</v>
       </c>
       <c r="D26">
-        <v>95</v>
+        <v>79.2</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F26">
         <v>95</v>
@@ -5440,40 +5440,40 @@
         <v>88.3</v>
       </c>
       <c r="H26">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I26">
+        <v>83.3</v>
+      </c>
+      <c r="J26">
+        <v>61.4</v>
+      </c>
+      <c r="K26">
+        <v>98</v>
+      </c>
+      <c r="L26">
         <v>85</v>
       </c>
-      <c r="I26">
-        <v>66.7</v>
-      </c>
-      <c r="J26">
-        <v>40</v>
-      </c>
-      <c r="K26">
-        <v>100</v>
-      </c>
-      <c r="L26">
-        <v>75</v>
-      </c>
       <c r="M26">
-        <v>86.7</v>
+        <v>79.5</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>61.4</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5481,16 +5481,16 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>100</v>
       </c>
       <c r="D27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E27">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -5505,34 +5505,34 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5540,16 +5540,16 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
       </c>
       <c r="D28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E28">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -5567,31 +5567,31 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L28">
         <v>100</v>
       </c>
       <c r="M28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5599,16 +5599,16 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C29">
         <v>100</v>
       </c>
       <c r="D29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E29">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -5617,7 +5617,7 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I29">
         <v>100</v>
@@ -5626,31 +5626,31 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5658,16 +5658,16 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C30">
         <v>100</v>
       </c>
       <c r="D30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E30">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F30">
         <v>95</v>
@@ -5676,40 +5676,40 @@
         <v>95</v>
       </c>
       <c r="H30">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I30">
         <v>100</v>
       </c>
       <c r="J30">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5717,16 +5717,16 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C31">
         <v>100</v>
       </c>
       <c r="D31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E31">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F31">
         <v>100</v>
@@ -5741,34 +5741,34 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L31">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M31">
-        <v>108.3</v>
+        <v>94.7</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5776,16 +5776,16 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="C32">
         <v>86.7</v>
       </c>
       <c r="D32">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="E32">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F32">
         <v>85</v>
@@ -5794,40 +5794,40 @@
         <v>83.3</v>
       </c>
       <c r="H32">
-        <v>55</v>
+        <v>70.5</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="J32">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L32">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="M32">
-        <v>83.3</v>
+        <v>75.8</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>70.5</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5835,16 +5835,16 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>100</v>
       </c>
       <c r="D33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E33">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -5853,7 +5853,7 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="I33">
         <v>100</v>
@@ -5862,31 +5862,31 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L33">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5894,16 +5894,16 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>100</v>
       </c>
       <c r="D34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E34">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F34">
         <v>100</v>
@@ -5912,40 +5912,40 @@
         <v>100</v>
       </c>
       <c r="H34">
-        <v>75</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I34">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L34">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M34">
-        <v>116.7</v>
+        <v>98.5</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5953,16 +5953,16 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="C35">
         <v>100</v>
       </c>
       <c r="D35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E35">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F35">
         <v>100</v>
@@ -5971,7 +5971,7 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>85</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I35">
         <v>100</v>
@@ -5980,31 +5980,31 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L35">
         <v>100</v>
       </c>
       <c r="M35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -6012,16 +6012,16 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C36">
         <v>100</v>
       </c>
       <c r="D36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E36">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F36">
         <v>100</v>
@@ -6030,40 +6030,40 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="I36">
         <v>100</v>
       </c>
       <c r="J36">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="K36">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L36">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -6071,16 +6071,16 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C37">
         <v>100</v>
       </c>
       <c r="D37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E37">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F37">
         <v>100</v>
@@ -6098,31 +6098,31 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L37">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -6130,16 +6130,16 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C38">
         <v>100</v>
       </c>
       <c r="D38">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E38">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F38">
         <v>95</v>
@@ -6148,7 +6148,7 @@
         <v>100</v>
       </c>
       <c r="H38">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I38">
         <v>100</v>
@@ -6157,31 +6157,31 @@
         <v>100</v>
       </c>
       <c r="K38">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L38">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M38">
-        <v>101.7</v>
+        <v>91.7</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -6189,16 +6189,16 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C39">
         <v>100</v>
       </c>
       <c r="D39">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="E39">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F39">
         <v>100</v>
@@ -6207,40 +6207,40 @@
         <v>100</v>
       </c>
       <c r="H39">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="I39">
         <v>100</v>
       </c>
       <c r="J39">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="K39">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L39">
         <v>100</v>
       </c>
       <c r="M39">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -6248,16 +6248,16 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C40">
         <v>100</v>
       </c>
       <c r="D40">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E40">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F40">
         <v>95</v>
@@ -6266,7 +6266,7 @@
         <v>100</v>
       </c>
       <c r="H40">
-        <v>80</v>
+        <v>77.3</v>
       </c>
       <c r="I40">
         <v>100</v>
@@ -6275,31 +6275,31 @@
         <v>100</v>
       </c>
       <c r="K40">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L40">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M40">
-        <v>113.3</v>
+        <v>97</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -6307,16 +6307,16 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="C41">
         <v>100</v>
       </c>
       <c r="D41">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="E41">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F41">
         <v>95</v>
@@ -6325,40 +6325,40 @@
         <v>88.3</v>
       </c>
       <c r="H41">
-        <v>70</v>
+        <v>81.8</v>
       </c>
       <c r="I41">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="J41">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="K41">
+        <v>98</v>
+      </c>
+      <c r="L41">
         <v>90</v>
       </c>
-      <c r="K41">
-        <v>100</v>
-      </c>
-      <c r="L41">
-        <v>85</v>
-      </c>
       <c r="M41">
-        <v>116.7</v>
+        <v>93.2</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -6366,16 +6366,16 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C42">
         <v>100</v>
       </c>
       <c r="D42">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E42">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F42">
         <v>100</v>
@@ -6393,31 +6393,31 @@
         <v>100</v>
       </c>
       <c r="K42">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L42">
         <v>100</v>
       </c>
       <c r="M42">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -6425,16 +6425,16 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C43">
         <v>100</v>
       </c>
       <c r="D43">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E43">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F43">
         <v>100</v>
@@ -6449,34 +6449,34 @@
         <v>100</v>
       </c>
       <c r="J43">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="K43">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L43">
         <v>100</v>
       </c>
       <c r="M43">
-        <v>116.7</v>
+        <v>98.5</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -6484,16 +6484,16 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C44">
         <v>100</v>
       </c>
       <c r="D44">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E44">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F44">
         <v>100</v>
@@ -6511,31 +6511,31 @@
         <v>100</v>
       </c>
       <c r="K44">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L44">
         <v>100</v>
       </c>
       <c r="M44">
-        <v>116.7</v>
+        <v>98.5</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -6543,16 +6543,16 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C45">
         <v>100</v>
       </c>
       <c r="D45">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E45">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="F45">
         <v>100</v>
@@ -6561,40 +6561,40 @@
         <v>85</v>
       </c>
       <c r="H45">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="I45">
         <v>100</v>
       </c>
       <c r="J45">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="K45">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L45">
         <v>100</v>
       </c>
       <c r="M45">
-        <v>110</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2BLCM - Estadisticos 20222.xlsx
+++ b/grupos/2BLCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -218,18 +218,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
+    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -251,10 +251,10 @@
     <t>SOLANO</t>
   </si>
   <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
@@ -266,10 +266,10 @@
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
   </si>
   <si>
     <t>OJEDA</t>
@@ -281,10 +281,10 @@
     <t>KEVIN</t>
   </si>
   <si>
-    <t>DARA NAOMI</t>
-  </si>
-  <si>
-    <t>KARENT LILIANA</t>
+    <t>MELISA VIANNEY</t>
+  </si>
+  <si>
+    <t>ESTEFANY CELESTE</t>
   </si>
   <si>
     <t>ABIGAIL ANTONIA</t>
@@ -819,10 +819,10 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -831,7 +831,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -840,7 +840,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -849,7 +849,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -896,10 +896,10 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -908,13 +908,13 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -973,10 +973,10 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -985,7 +985,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>5</v>
@@ -1050,10 +1050,10 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1062,13 +1062,13 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>6</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -1127,10 +1127,10 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1139,7 +1139,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>6</v>
@@ -1148,7 +1148,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1204,10 +1204,10 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1216,7 +1216,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>7</v>
@@ -1225,7 +1225,7 @@
         <v>6</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1234,7 +1234,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1281,10 +1281,10 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1293,7 +1293,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T10">
         <v>5</v>
@@ -1358,10 +1358,10 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1370,16 +1370,16 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>7</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1435,10 +1435,10 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1447,7 +1447,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1512,10 +1512,10 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>6</v>
@@ -1533,7 +1533,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1542,7 +1542,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1589,10 +1589,10 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1601,16 +1601,16 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>7</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1619,7 +1619,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1666,10 +1666,10 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1678,7 +1678,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>5</v>
@@ -1687,7 +1687,7 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1696,7 +1696,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1743,10 +1743,10 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -1755,16 +1755,16 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>6</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1820,10 +1820,10 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -1832,7 +1832,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>5</v>
@@ -1850,7 +1850,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1897,10 +1897,10 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -1909,16 +1909,16 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>6</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -1927,7 +1927,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1974,10 +1974,10 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -1986,7 +1986,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2051,10 +2051,10 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2063,7 +2063,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2072,7 +2072,7 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2128,10 +2128,10 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2140,7 +2140,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>5</v>
@@ -2205,10 +2205,10 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2217,13 +2217,13 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>5</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2282,10 +2282,10 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2294,7 +2294,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>5</v>
@@ -2359,10 +2359,10 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2371,7 +2371,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -2380,7 +2380,7 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2389,7 +2389,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2436,10 +2436,10 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2448,7 +2448,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2513,10 +2513,10 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2525,7 +2525,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
         <v>5</v>
@@ -2590,10 +2590,10 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2602,7 +2602,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>7</v>
@@ -2620,7 +2620,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2667,10 +2667,10 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2679,7 +2679,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -2697,7 +2697,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2744,10 +2744,10 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -2756,7 +2756,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -2821,10 +2821,10 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -2833,7 +2833,7 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>6</v>
@@ -2898,10 +2898,10 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -2910,7 +2910,7 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>7</v>
@@ -2975,10 +2975,10 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -2987,16 +2987,16 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
         <v>5</v>
       </c>
       <c r="U32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -3052,10 +3052,10 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3064,13 +3064,13 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>8</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>9</v>
@@ -3129,10 +3129,10 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3141,13 +3141,13 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>6</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>10</v>
@@ -3159,7 +3159,7 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3206,10 +3206,10 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3218,13 +3218,13 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>7</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>7</v>
@@ -3283,10 +3283,10 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -3295,7 +3295,7 @@
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>5</v>
@@ -3360,10 +3360,10 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -3372,7 +3372,7 @@
         <v>-1</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
         <v>5</v>
@@ -3390,7 +3390,7 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3437,10 +3437,10 @@
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -3449,7 +3449,7 @@
         <v>-1</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>6</v>
@@ -3458,7 +3458,7 @@
         <v>6</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W38">
         <v>7</v>
@@ -3467,7 +3467,7 @@
         <v>7</v>
       </c>
       <c r="Y38">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3514,10 +3514,10 @@
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -3526,13 +3526,13 @@
         <v>-1</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
         <v>7</v>
       </c>
       <c r="U39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V39">
         <v>7</v>
@@ -3591,10 +3591,10 @@
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -3603,7 +3603,7 @@
         <v>-1</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T40">
         <v>6</v>
@@ -3621,7 +3621,7 @@
         <v>5</v>
       </c>
       <c r="Y40">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3668,10 +3668,10 @@
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -3680,7 +3680,7 @@
         <v>-1</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T41">
         <v>5</v>
@@ -3745,10 +3745,10 @@
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q42">
         <v>-1</v>
@@ -3757,13 +3757,13 @@
         <v>-1</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T42">
         <v>7</v>
       </c>
       <c r="U42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V42">
         <v>8</v>
@@ -3822,10 +3822,10 @@
         <v>-1</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q43">
         <v>-1</v>
@@ -3834,16 +3834,16 @@
         <v>-1</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T43">
         <v>7</v>
       </c>
       <c r="U43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W43">
         <v>7</v>
@@ -3852,7 +3852,7 @@
         <v>8</v>
       </c>
       <c r="Y43">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3899,10 +3899,10 @@
         <v>-1</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q44">
         <v>-1</v>
@@ -3911,7 +3911,7 @@
         <v>-1</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T44">
         <v>8</v>
@@ -3976,10 +3976,10 @@
         <v>-1</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q45">
         <v>-1</v>
@@ -3988,16 +3988,16 @@
         <v>-1</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T45">
         <v>6</v>
       </c>
       <c r="U45">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W45">
         <v>9</v>
@@ -4006,7 +4006,7 @@
         <v>9</v>
       </c>
       <c r="Y45">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4166,7 +4166,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q4">
         <v>98</v>
@@ -4175,7 +4175,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4225,7 +4225,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q5">
         <v>98</v>
@@ -4234,7 +4234,7 @@
         <v>97.5</v>
       </c>
       <c r="S5">
-        <v>91.7</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -4281,10 +4281,10 @@
         <v>75</v>
       </c>
       <c r="O6">
-        <v>83.3</v>
+        <v>54.2</v>
       </c>
       <c r="P6">
-        <v>45.5</v>
+        <v>34.4</v>
       </c>
       <c r="Q6">
         <v>98</v>
@@ -4293,7 +4293,7 @@
         <v>72.5</v>
       </c>
       <c r="S6">
-        <v>74.2</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4343,7 +4343,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>90.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q7">
         <v>98</v>
@@ -4352,7 +4352,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>91.7</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4399,10 +4399,10 @@
         <v>95.5</v>
       </c>
       <c r="O8">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="P8">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q8">
         <v>98</v>
@@ -4411,7 +4411,7 @@
         <v>97.5</v>
       </c>
       <c r="S8">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4461,7 +4461,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q9">
         <v>98</v>
@@ -4470,7 +4470,7 @@
         <v>90</v>
       </c>
       <c r="S9">
-        <v>89.40000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4517,10 +4517,10 @@
         <v>56.8</v>
       </c>
       <c r="O10">
-        <v>83.3</v>
+        <v>52.1</v>
       </c>
       <c r="P10">
-        <v>31.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q10">
         <v>98</v>
@@ -4529,7 +4529,7 @@
         <v>47.5</v>
       </c>
       <c r="S10">
-        <v>33.3</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4694,7 +4694,7 @@
         <v>95.5</v>
       </c>
       <c r="O13">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -4706,7 +4706,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>91.7</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4765,7 +4765,7 @@
         <v>95</v>
       </c>
       <c r="S14">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4812,10 +4812,10 @@
         <v>93.2</v>
       </c>
       <c r="O15">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="P15">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q15">
         <v>98</v>
@@ -4824,7 +4824,7 @@
         <v>95</v>
       </c>
       <c r="S15">
-        <v>83.3</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4883,7 +4883,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4930,10 +4930,10 @@
         <v>72.7</v>
       </c>
       <c r="O17">
-        <v>90</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="P17">
-        <v>81.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="Q17">
         <v>98</v>
@@ -4942,7 +4942,7 @@
         <v>90</v>
       </c>
       <c r="S17">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4989,10 +4989,10 @@
         <v>93.2</v>
       </c>
       <c r="O18">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="P18">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="Q18">
         <v>98</v>
@@ -5166,10 +5166,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="O21">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="P21">
-        <v>68.2</v>
+        <v>56.3</v>
       </c>
       <c r="Q21">
         <v>98</v>
@@ -5178,7 +5178,7 @@
         <v>57.5</v>
       </c>
       <c r="S21">
-        <v>85.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -5225,10 +5225,10 @@
         <v>68.2</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="P22">
-        <v>31.8</v>
+        <v>25</v>
       </c>
       <c r="Q22">
         <v>98</v>
@@ -5237,7 +5237,7 @@
         <v>65</v>
       </c>
       <c r="S22">
-        <v>75.8</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -5284,10 +5284,10 @@
         <v>86.40000000000001</v>
       </c>
       <c r="O23">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="P23">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q23">
         <v>98</v>
@@ -5296,7 +5296,7 @@
         <v>85</v>
       </c>
       <c r="S23">
-        <v>86.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5346,7 +5346,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -5355,7 +5355,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5461,10 +5461,10 @@
         <v>88.59999999999999</v>
       </c>
       <c r="O26">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="P26">
-        <v>61.4</v>
+        <v>48.4</v>
       </c>
       <c r="Q26">
         <v>98</v>
@@ -5473,7 +5473,7 @@
         <v>85</v>
       </c>
       <c r="S26">
-        <v>79.5</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5523,7 +5523,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q27">
         <v>98</v>
@@ -5700,7 +5700,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>95.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q30">
         <v>98</v>
@@ -5709,7 +5709,7 @@
         <v>97.5</v>
       </c>
       <c r="S30">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5759,7 +5759,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q31">
         <v>98</v>
@@ -5768,7 +5768,7 @@
         <v>97.5</v>
       </c>
       <c r="S31">
-        <v>94.7</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5815,10 +5815,10 @@
         <v>70.5</v>
       </c>
       <c r="O32">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="P32">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q32">
         <v>98</v>
@@ -5827,7 +5827,7 @@
         <v>65</v>
       </c>
       <c r="S32">
-        <v>75.8</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5877,7 +5877,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q33">
         <v>98</v>
@@ -5933,10 +5933,10 @@
         <v>88.59999999999999</v>
       </c>
       <c r="O34">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="P34">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q34">
         <v>98</v>
@@ -5945,7 +5945,7 @@
         <v>95</v>
       </c>
       <c r="S34">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5995,7 +5995,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q35">
         <v>98</v>
@@ -6054,7 +6054,7 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q36">
         <v>98</v>
@@ -6113,7 +6113,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q37">
         <v>98</v>
@@ -6172,7 +6172,7 @@
         <v>100</v>
       </c>
       <c r="P38">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q38">
         <v>98</v>
@@ -6181,7 +6181,7 @@
         <v>90</v>
       </c>
       <c r="S38">
-        <v>91.7</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -6228,10 +6228,10 @@
         <v>95.5</v>
       </c>
       <c r="O39">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P39">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q39">
         <v>98</v>
@@ -6299,7 +6299,7 @@
         <v>90</v>
       </c>
       <c r="S40">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -6346,10 +6346,10 @@
         <v>81.8</v>
       </c>
       <c r="O41">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P41">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q41">
         <v>98</v>
@@ -6467,7 +6467,7 @@
         <v>100</v>
       </c>
       <c r="P43">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q43">
         <v>98</v>
@@ -6476,7 +6476,7 @@
         <v>100</v>
       </c>
       <c r="S43">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -6535,7 +6535,7 @@
         <v>100</v>
       </c>
       <c r="S44">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -6585,7 +6585,7 @@
         <v>100</v>
       </c>
       <c r="P45">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q45">
         <v>98</v>
@@ -6594,7 +6594,7 @@
         <v>100</v>
       </c>
       <c r="S45">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
     </row>
   </sheetData>
@@ -6651,7 +6651,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
@@ -6660,19 +6660,19 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>69</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>31</v>
+        <v>28.6</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6683,7 +6683,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -6692,19 +6692,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2">
-        <v>71.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="G3" s="2">
-        <v>28.6</v>
+        <v>23.8</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6715,7 +6715,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -6724,19 +6724,19 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2">
-        <v>71.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>28.6</v>
+        <v>21.4</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
@@ -6756,19 +6756,19 @@
         <v>42</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2">
-        <v>78.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="G5" s="2">
-        <v>21.4</v>
+        <v>19</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6832,7 +6832,7 @@
         <v>14.3</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6882,7 +6882,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6929,7 +6929,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6952,7 +6952,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6960,7 +6960,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920344</v>
+        <v>22330051920145</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
@@ -6975,7 +6975,7 @@
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6983,19 +6983,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920128</v>
+        <v>22330051920145</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>68</v>
@@ -7006,22 +7006,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920130</v>
+        <v>22330051920126</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7029,24 +7029,47 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
+        <v>22330051920130</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
         <v>22330051920353</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>80</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>85</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>90</v>
       </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7">
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2BLCM - Estadisticos 20222.xlsx
+++ b/grupos/2BLCM - Estadisticos 20222.xlsx
@@ -230,10 +230,10 @@
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>NC</t>
@@ -825,7 +825,7 @@
         <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -843,7 +843,7 @@
         <v>6</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -902,7 +902,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -920,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -979,7 +979,7 @@
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1056,7 +1056,7 @@
         <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1074,7 +1074,7 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1133,7 +1133,7 @@
         <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1151,7 +1151,7 @@
         <v>6</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1210,7 +1210,7 @@
         <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1228,7 +1228,7 @@
         <v>6</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1287,7 +1287,7 @@
         <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1364,7 +1364,7 @@
         <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1441,7 +1441,7 @@
         <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1518,7 +1518,7 @@
         <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1595,7 +1595,7 @@
         <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1672,7 +1672,7 @@
         <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1749,7 +1749,7 @@
         <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1826,7 +1826,7 @@
         <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -1903,7 +1903,7 @@
         <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -1921,7 +1921,7 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -1980,7 +1980,7 @@
         <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2057,7 +2057,7 @@
         <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2134,7 +2134,7 @@
         <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2152,7 +2152,7 @@
         <v>5</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2211,7 +2211,7 @@
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2288,7 +2288,7 @@
         <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2365,7 +2365,7 @@
         <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2442,7 +2442,7 @@
         <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2519,7 +2519,7 @@
         <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2596,7 +2596,7 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2673,7 +2673,7 @@
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2750,7 +2750,7 @@
         <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -2827,7 +2827,7 @@
         <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -2904,7 +2904,7 @@
         <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -2981,7 +2981,7 @@
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -2999,7 +2999,7 @@
         <v>6</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -3058,7 +3058,7 @@
         <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3076,7 +3076,7 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3135,7 +3135,7 @@
         <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3212,7 +3212,7 @@
         <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -3230,7 +3230,7 @@
         <v>7</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>8</v>
@@ -3289,7 +3289,7 @@
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3307,7 +3307,7 @@
         <v>7</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>9</v>
@@ -3366,7 +3366,7 @@
         <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -3384,7 +3384,7 @@
         <v>5</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X37">
         <v>6</v>
@@ -3443,7 +3443,7 @@
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -3461,7 +3461,7 @@
         <v>7</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>7</v>
@@ -3520,7 +3520,7 @@
         <v>7</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -3538,7 +3538,7 @@
         <v>7</v>
       </c>
       <c r="W39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X39">
         <v>8</v>
@@ -3597,7 +3597,7 @@
         <v>6</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -3615,7 +3615,7 @@
         <v>5</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X40">
         <v>5</v>
@@ -3674,7 +3674,7 @@
         <v>6</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R41">
         <v>-1</v>
@@ -3751,7 +3751,7 @@
         <v>10</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>-1</v>
@@ -3828,7 +3828,7 @@
         <v>8</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R43">
         <v>-1</v>
@@ -3905,7 +3905,7 @@
         <v>10</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R44">
         <v>-1</v>
@@ -3982,7 +3982,7 @@
         <v>10</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R45">
         <v>-1</v>
@@ -4169,7 +4169,7 @@
         <v>93.8</v>
       </c>
       <c r="Q4">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -4228,7 +4228,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="Q5">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R5">
         <v>97.5</v>
@@ -4287,7 +4287,7 @@
         <v>34.4</v>
       </c>
       <c r="Q6">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R6">
         <v>72.5</v>
@@ -4346,7 +4346,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="Q7">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -4405,7 +4405,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q8">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R8">
         <v>97.5</v>
@@ -4464,7 +4464,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q9">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R9">
         <v>90</v>
@@ -4523,7 +4523,7 @@
         <v>21.9</v>
       </c>
       <c r="Q10">
-        <v>98</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="R10">
         <v>47.5</v>
@@ -4582,7 +4582,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -4641,7 +4641,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -4700,7 +4700,7 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -4759,7 +4759,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R14">
         <v>95</v>
@@ -4818,7 +4818,7 @@
         <v>93.8</v>
       </c>
       <c r="Q15">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R15">
         <v>95</v>
@@ -4877,7 +4877,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -4936,7 +4936,7 @@
         <v>64.09999999999999</v>
       </c>
       <c r="Q17">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R17">
         <v>90</v>
@@ -4995,7 +4995,7 @@
         <v>93.8</v>
       </c>
       <c r="Q18">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -5054,7 +5054,7 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -5113,7 +5113,7 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -5172,7 +5172,7 @@
         <v>56.3</v>
       </c>
       <c r="Q21">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R21">
         <v>57.5</v>
@@ -5231,7 +5231,7 @@
         <v>25</v>
       </c>
       <c r="Q22">
-        <v>98</v>
+        <v>65.8</v>
       </c>
       <c r="R22">
         <v>65</v>
@@ -5290,7 +5290,7 @@
         <v>93.8</v>
       </c>
       <c r="Q23">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R23">
         <v>85</v>
@@ -5408,7 +5408,7 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -5467,7 +5467,7 @@
         <v>48.4</v>
       </c>
       <c r="Q26">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R26">
         <v>85</v>
@@ -5526,7 +5526,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q27">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5585,7 +5585,7 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -5644,7 +5644,7 @@
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -5703,7 +5703,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="Q30">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R30">
         <v>97.5</v>
@@ -5762,7 +5762,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q31">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R31">
         <v>97.5</v>
@@ -5821,7 +5821,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="Q32">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R32">
         <v>65</v>
@@ -5880,7 +5880,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q33">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R33">
         <v>97.5</v>
@@ -5939,7 +5939,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q34">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R34">
         <v>95</v>
@@ -5998,7 +5998,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q35">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R35">
         <v>100</v>
@@ -6057,7 +6057,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q36">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R36">
         <v>97.5</v>
@@ -6116,7 +6116,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q37">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R37">
         <v>97.5</v>
@@ -6175,7 +6175,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q38">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R38">
         <v>90</v>
@@ -6234,7 +6234,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q39">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R39">
         <v>100</v>
@@ -6293,7 +6293,7 @@
         <v>100</v>
       </c>
       <c r="Q40">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R40">
         <v>90</v>
@@ -6352,7 +6352,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="Q41">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R41">
         <v>90</v>
@@ -6411,7 +6411,7 @@
         <v>100</v>
       </c>
       <c r="Q42">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R42">
         <v>100</v>
@@ -6470,7 +6470,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q43">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R43">
         <v>100</v>
@@ -6529,7 +6529,7 @@
         <v>100</v>
       </c>
       <c r="Q44">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R44">
         <v>100</v>
@@ -6588,7 +6588,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q45">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="R45">
         <v>100</v>
@@ -6779,7 +6779,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
@@ -6788,16 +6788,16 @@
         <v>42</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>83.3</v>
+        <v>85.7</v>
       </c>
       <c r="G6" s="2">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="H6">
         <v>7.7</v>
@@ -6811,7 +6811,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -6832,7 +6832,7 @@
         <v>14.3</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/2BLCM - Estadisticos 20222.xlsx
+++ b/grupos/2BLCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="96">
   <si>
     <t>Materia</t>
   </si>
@@ -248,49 +248,64 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ARZATE</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
+    <t>TENORIO</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>LUCIANA</t>
+  </si>
+  <si>
+    <t>ABIGAIL ANTONIA</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>ZURI GABRIELA</t>
+  </si>
+  <si>
+    <t>AZUL ARIADNA</t>
   </si>
   <si>
     <t>KEVIN</t>
   </si>
   <si>
-    <t>MELISA VIANNEY</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
-  </si>
-  <si>
-    <t>ABIGAIL ANTONIA</t>
-  </si>
-  <si>
-    <t>AZUL ARIADNA</t>
+    <t>ORESTES</t>
   </si>
 </sst>
 </file>
@@ -816,7 +831,7 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
         <v>9</v>
@@ -828,13 +843,13 @@
         <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>7</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -846,7 +861,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -893,7 +908,7 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>8</v>
@@ -905,7 +920,7 @@
         <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>7</v>
@@ -970,7 +985,7 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>5</v>
@@ -982,7 +997,7 @@
         <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
         <v>5</v>
@@ -1047,7 +1062,7 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -1059,13 +1074,13 @@
         <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>10</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1124,7 +1139,7 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>10</v>
@@ -1136,7 +1151,7 @@
         <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>8</v>
@@ -1201,7 +1216,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1213,13 +1228,13 @@
         <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>7</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>6</v>
@@ -1231,7 +1246,7 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1278,7 +1293,7 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -1290,7 +1305,7 @@
         <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1355,7 +1370,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>7</v>
@@ -1367,13 +1382,13 @@
         <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>9</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -1432,7 +1447,7 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>10</v>
@@ -1444,7 +1459,7 @@
         <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>10</v>
@@ -1509,7 +1524,7 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>7</v>
@@ -1521,7 +1536,7 @@
         <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>8</v>
@@ -1586,7 +1601,7 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>8</v>
@@ -1598,13 +1613,13 @@
         <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>10</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1663,7 +1678,7 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>8</v>
@@ -1675,7 +1690,7 @@
         <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>9</v>
@@ -1740,7 +1755,7 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -1752,7 +1767,7 @@
         <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>8</v>
@@ -1817,7 +1832,7 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -1829,7 +1844,7 @@
         <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
         <v>8</v>
@@ -1894,7 +1909,7 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>5</v>
@@ -1906,13 +1921,13 @@
         <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>8</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -1971,7 +1986,7 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>10</v>
@@ -1983,7 +1998,7 @@
         <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>10</v>
@@ -2048,7 +2063,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>10</v>
@@ -2060,7 +2075,7 @@
         <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>10</v>
@@ -2125,7 +2140,7 @@
         <v>3</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2137,7 +2152,7 @@
         <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>7</v>
@@ -2202,7 +2217,7 @@
         <v>3</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -2214,7 +2229,7 @@
         <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
         <v>5</v>
@@ -2279,7 +2294,7 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
         <v>6</v>
@@ -2291,7 +2306,7 @@
         <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
         <v>5</v>
@@ -2309,7 +2324,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2356,7 +2371,7 @@
         <v>4</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>8</v>
@@ -2368,13 +2383,13 @@
         <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
         <v>8</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2386,7 +2401,7 @@
         <v>7</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2433,7 +2448,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
         <v>10</v>
@@ -2445,7 +2460,7 @@
         <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>10</v>
@@ -2510,7 +2525,7 @@
         <v>3</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>5</v>
@@ -2522,7 +2537,7 @@
         <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
         <v>5</v>
@@ -2540,7 +2555,7 @@
         <v>5</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2587,7 +2602,7 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>9</v>
@@ -2599,13 +2614,13 @@
         <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>10</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>9</v>
@@ -2664,7 +2679,7 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
         <v>10</v>
@@ -2676,13 +2691,13 @@
         <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>10</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2741,7 +2756,7 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>9</v>
@@ -2753,7 +2768,7 @@
         <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>10</v>
@@ -2818,7 +2833,7 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>7</v>
@@ -2830,13 +2845,13 @@
         <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
         <v>7</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U30">
         <v>7</v>
@@ -2895,7 +2910,7 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>8</v>
@@ -2907,13 +2922,13 @@
         <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>8</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U31">
         <v>8</v>
@@ -2972,7 +2987,7 @@
         <v>3</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>7</v>
@@ -2984,7 +2999,7 @@
         <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
         <v>5</v>
@@ -3049,7 +3064,7 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <v>6</v>
@@ -3061,13 +3076,13 @@
         <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
         <v>10</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>8</v>
@@ -3126,7 +3141,7 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
         <v>6</v>
@@ -3138,7 +3153,7 @@
         <v>8</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
         <v>8</v>
@@ -3156,7 +3171,7 @@
         <v>9</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -3203,7 +3218,7 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <v>9</v>
@@ -3215,13 +3230,13 @@
         <v>9</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
         <v>8</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>9</v>
@@ -3280,7 +3295,7 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
         <v>7</v>
@@ -3292,7 +3307,7 @@
         <v>6</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
         <v>10</v>
@@ -3357,7 +3372,7 @@
         <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
         <v>8</v>
@@ -3369,13 +3384,13 @@
         <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S37">
         <v>9</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U37">
         <v>9</v>
@@ -3434,7 +3449,7 @@
         <v>7</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O38">
         <v>6</v>
@@ -3446,13 +3461,13 @@
         <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S38">
         <v>10</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U38">
         <v>6</v>
@@ -3464,7 +3479,7 @@
         <v>8</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>8</v>
@@ -3511,7 +3526,7 @@
         <v>9</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O39">
         <v>8</v>
@@ -3523,13 +3538,13 @@
         <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S39">
         <v>8</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U39">
         <v>9</v>
@@ -3588,7 +3603,7 @@
         <v>8</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -3600,13 +3615,13 @@
         <v>6</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S40">
         <v>7</v>
       </c>
       <c r="T40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>6</v>
@@ -3665,7 +3680,7 @@
         <v>3</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O41">
         <v>6</v>
@@ -3677,7 +3692,7 @@
         <v>5</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S41">
         <v>5</v>
@@ -3742,7 +3757,7 @@
         <v>8</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>7</v>
@@ -3754,13 +3769,13 @@
         <v>10</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S42">
         <v>10</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U42">
         <v>8</v>
@@ -3819,7 +3834,7 @@
         <v>9</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O43">
         <v>8</v>
@@ -3831,13 +3846,13 @@
         <v>8</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S43">
         <v>7</v>
       </c>
       <c r="T43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U43">
         <v>8</v>
@@ -3896,7 +3911,7 @@
         <v>10</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O44">
         <v>10</v>
@@ -3908,13 +3923,13 @@
         <v>10</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S44">
         <v>10</v>
       </c>
       <c r="T44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U44">
         <v>10</v>
@@ -3973,7 +3988,7 @@
         <v>7</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O45">
         <v>7</v>
@@ -3985,7 +4000,7 @@
         <v>10</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S45">
         <v>9</v>
@@ -4003,7 +4018,7 @@
         <v>9</v>
       </c>
       <c r="X45">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y45">
         <v>8</v>
@@ -4160,7 +4175,7 @@
         <v>97.7</v>
       </c>
       <c r="N4">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -4172,7 +4187,7 @@
         <v>98.7</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S4">
         <v>98.40000000000001</v>
@@ -4219,7 +4234,7 @@
         <v>91.7</v>
       </c>
       <c r="N5">
-        <v>86.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -4231,7 +4246,7 @@
         <v>98.7</v>
       </c>
       <c r="R5">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S5">
         <v>94.3</v>
@@ -4278,7 +4293,7 @@
         <v>74.2</v>
       </c>
       <c r="N6">
-        <v>75</v>
+        <v>67.2</v>
       </c>
       <c r="O6">
         <v>54.2</v>
@@ -4290,7 +4305,7 @@
         <v>98.7</v>
       </c>
       <c r="R6">
-        <v>72.5</v>
+        <v>53.1</v>
       </c>
       <c r="S6">
         <v>77.09999999999999</v>
@@ -4337,7 +4352,7 @@
         <v>91.7</v>
       </c>
       <c r="N7">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -4349,7 +4364,7 @@
         <v>98.7</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S7">
         <v>94.3</v>
@@ -4396,7 +4411,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N8">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O8">
         <v>93.8</v>
@@ -4408,7 +4423,7 @@
         <v>98.7</v>
       </c>
       <c r="R8">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S8">
         <v>93.8</v>
@@ -4455,7 +4470,7 @@
         <v>89.40000000000001</v>
       </c>
       <c r="N9">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -4467,7 +4482,7 @@
         <v>98.7</v>
       </c>
       <c r="R9">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="S9">
         <v>92.7</v>
@@ -4514,7 +4529,7 @@
         <v>33.3</v>
       </c>
       <c r="N10">
-        <v>56.8</v>
+        <v>39.1</v>
       </c>
       <c r="O10">
         <v>52.1</v>
@@ -4526,7 +4541,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R10">
-        <v>47.5</v>
+        <v>29.7</v>
       </c>
       <c r="S10">
         <v>22.9</v>
@@ -4573,7 +4588,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -4691,7 +4706,7 @@
         <v>91.7</v>
       </c>
       <c r="N13">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O13">
         <v>93.8</v>
@@ -4762,7 +4777,7 @@
         <v>98.7</v>
       </c>
       <c r="R14">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S14">
         <v>96.90000000000001</v>
@@ -4809,7 +4824,7 @@
         <v>83.3</v>
       </c>
       <c r="N15">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="O15">
         <v>95.8</v>
@@ -4821,7 +4836,7 @@
         <v>98.7</v>
       </c>
       <c r="R15">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S15">
         <v>88.5</v>
@@ -4868,7 +4883,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N16">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -4927,7 +4942,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N17">
-        <v>72.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="O17">
         <v>89.59999999999999</v>
@@ -4939,7 +4954,7 @@
         <v>98.7</v>
       </c>
       <c r="R17">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S17">
         <v>93.8</v>
@@ -4986,7 +5001,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="O18">
         <v>95.8</v>
@@ -4998,7 +5013,7 @@
         <v>98.7</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -5104,7 +5119,7 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -5163,7 +5178,7 @@
         <v>85.59999999999999</v>
       </c>
       <c r="N21">
-        <v>65.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="O21">
         <v>87.5</v>
@@ -5175,7 +5190,7 @@
         <v>98.7</v>
       </c>
       <c r="R21">
-        <v>57.5</v>
+        <v>70.3</v>
       </c>
       <c r="S21">
         <v>90.09999999999999</v>
@@ -5222,7 +5237,7 @@
         <v>75.8</v>
       </c>
       <c r="N22">
-        <v>68.2</v>
+        <v>46.9</v>
       </c>
       <c r="O22">
         <v>68.8</v>
@@ -5234,7 +5249,7 @@
         <v>65.8</v>
       </c>
       <c r="R22">
-        <v>65</v>
+        <v>48.4</v>
       </c>
       <c r="S22">
         <v>57.3</v>
@@ -5281,7 +5296,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="N23">
-        <v>86.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="O23">
         <v>91.7</v>
@@ -5293,7 +5308,7 @@
         <v>98.7</v>
       </c>
       <c r="R23">
-        <v>85</v>
+        <v>67.2</v>
       </c>
       <c r="S23">
         <v>85.40000000000001</v>
@@ -5340,7 +5355,7 @@
         <v>93.2</v>
       </c>
       <c r="N24">
-        <v>79.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -5458,7 +5473,7 @@
         <v>79.5</v>
       </c>
       <c r="N26">
-        <v>88.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O26">
         <v>75</v>
@@ -5470,7 +5485,7 @@
         <v>98.7</v>
       </c>
       <c r="R26">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S26">
         <v>80.7</v>
@@ -5635,7 +5650,7 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -5694,7 +5709,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="N30">
-        <v>97.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O30">
         <v>100</v>
@@ -5706,7 +5721,7 @@
         <v>98.7</v>
       </c>
       <c r="R30">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S30">
         <v>92.2</v>
@@ -5753,7 +5768,7 @@
         <v>94.7</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O31">
         <v>100</v>
@@ -5765,7 +5780,7 @@
         <v>98.7</v>
       </c>
       <c r="R31">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S31">
         <v>96.40000000000001</v>
@@ -5812,7 +5827,7 @@
         <v>75.8</v>
       </c>
       <c r="N32">
-        <v>70.5</v>
+        <v>70.3</v>
       </c>
       <c r="O32">
         <v>87.5</v>
@@ -5824,7 +5839,7 @@
         <v>98.7</v>
       </c>
       <c r="R32">
-        <v>65</v>
+        <v>56.3</v>
       </c>
       <c r="S32">
         <v>78.09999999999999</v>
@@ -5871,7 +5886,7 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>93.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O33">
         <v>100</v>
@@ -5883,7 +5898,7 @@
         <v>98.7</v>
       </c>
       <c r="R33">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -5930,7 +5945,7 @@
         <v>98.5</v>
       </c>
       <c r="N34">
-        <v>88.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="O34">
         <v>95.8</v>
@@ -5942,7 +5957,7 @@
         <v>98.7</v>
       </c>
       <c r="R34">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="S34">
         <v>99</v>
@@ -5989,7 +6004,7 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O35">
         <v>100</v>
@@ -6048,7 +6063,7 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="O36">
         <v>100</v>
@@ -6060,7 +6075,7 @@
         <v>98.7</v>
       </c>
       <c r="R36">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -6107,7 +6122,7 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O37">
         <v>100</v>
@@ -6119,7 +6134,7 @@
         <v>98.7</v>
       </c>
       <c r="R37">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S37">
         <v>100</v>
@@ -6166,7 +6181,7 @@
         <v>91.7</v>
       </c>
       <c r="N38">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O38">
         <v>100</v>
@@ -6178,7 +6193,7 @@
         <v>98.7</v>
       </c>
       <c r="R38">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="S38">
         <v>94.3</v>
@@ -6225,7 +6240,7 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O39">
         <v>93.8</v>
@@ -6237,7 +6252,7 @@
         <v>98.7</v>
       </c>
       <c r="R39">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S39">
         <v>100</v>
@@ -6284,7 +6299,7 @@
         <v>97</v>
       </c>
       <c r="N40">
-        <v>77.3</v>
+        <v>81.3</v>
       </c>
       <c r="O40">
         <v>100</v>
@@ -6296,7 +6311,7 @@
         <v>98.7</v>
       </c>
       <c r="R40">
-        <v>90</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S40">
         <v>97.90000000000001</v>
@@ -6343,7 +6358,7 @@
         <v>93.2</v>
       </c>
       <c r="N41">
-        <v>81.8</v>
+        <v>81.3</v>
       </c>
       <c r="O41">
         <v>97.90000000000001</v>
@@ -6355,7 +6370,7 @@
         <v>98.7</v>
       </c>
       <c r="R41">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S41">
         <v>93.2</v>
@@ -6579,7 +6594,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="N45">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="O45">
         <v>100</v>
@@ -6591,7 +6606,7 @@
         <v>98.7</v>
       </c>
       <c r="R45">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S45">
         <v>92.2</v>
@@ -6660,19 +6675,19 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F2" s="2">
-        <v>71.40000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="G2" s="2">
-        <v>28.6</v>
+        <v>38.1</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6724,19 +6739,19 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2">
-        <v>78.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="G4" s="2">
-        <v>21.4</v>
+        <v>23.8</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6914,16 +6929,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920354</v>
+        <v>22330051920343</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6937,22 +6952,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920354</v>
+        <v>22330051920130</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6960,22 +6975,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920145</v>
+        <v>22330051920133</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6983,22 +6998,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920145</v>
+        <v>22330051920138</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7006,22 +7021,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920126</v>
+        <v>22330051920353</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7029,22 +7044,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920130</v>
+        <v>22330051920354</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7052,16 +7067,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920353</v>
+        <v>22330051920143</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
